--- a/artfynd/A 57458-2025 artfynd.xlsx
+++ b/artfynd/A 57458-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130091945</v>
+        <v>130091975</v>
       </c>
       <c r="B2" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557675</v>
+        <v>557681</v>
       </c>
       <c r="R2" t="n">
-        <v>6977245</v>
+        <v>6977020</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130091975</v>
+        <v>130091945</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557681</v>
+        <v>557675</v>
       </c>
       <c r="R3" t="n">
-        <v>6977020</v>
+        <v>6977245</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130091926</v>
+        <v>130091960</v>
       </c>
       <c r="B6" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557842</v>
+        <v>557676</v>
       </c>
       <c r="R6" t="n">
-        <v>6977126</v>
+        <v>6977079</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130091960</v>
+        <v>130091922</v>
       </c>
       <c r="B7" t="n">
-        <v>80194</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557676</v>
+        <v>558032</v>
       </c>
       <c r="R7" t="n">
-        <v>6977079</v>
+        <v>6977158</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,7 +1272,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130091922</v>
+        <v>130091926</v>
       </c>
       <c r="B8" t="n">
         <v>57740</v>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558032</v>
+        <v>557842</v>
       </c>
       <c r="R8" t="n">
-        <v>6977158</v>
+        <v>6977126</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130091904</v>
+        <v>130091909</v>
       </c>
       <c r="B9" t="n">
         <v>57740</v>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557758</v>
+        <v>558154</v>
       </c>
       <c r="R9" t="n">
-        <v>6977187</v>
+        <v>6977116</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,7 +1476,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130091909</v>
+        <v>130091904</v>
       </c>
       <c r="B10" t="n">
         <v>57740</v>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558154</v>
+        <v>557758</v>
       </c>
       <c r="R10" t="n">
-        <v>6977116</v>
+        <v>6977187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130091916</v>
+        <v>130091952</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558130</v>
+        <v>557819</v>
       </c>
       <c r="R12" t="n">
-        <v>6977159</v>
+        <v>6977105</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,11 +1746,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130091952</v>
+        <v>130091916</v>
       </c>
       <c r="B13" t="n">
-        <v>80194</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557819</v>
+        <v>558130</v>
       </c>
       <c r="R13" t="n">
-        <v>6977105</v>
+        <v>6977159</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,6 +1843,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1976,32 +1976,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130091933</v>
+        <v>130091967</v>
       </c>
       <c r="B15" t="n">
-        <v>57740</v>
+        <v>80230</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557693</v>
+        <v>557677</v>
       </c>
       <c r="R15" t="n">
-        <v>6977096</v>
+        <v>6977026</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,11 +2047,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,32 +2073,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130091967</v>
+        <v>130091933</v>
       </c>
       <c r="B16" t="n">
-        <v>80230</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557677</v>
+        <v>557693</v>
       </c>
       <c r="R16" t="n">
-        <v>6977026</v>
+        <v>6977096</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2149,6 +2144,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2175,7 +2175,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130091924</v>
+        <v>130091930</v>
       </c>
       <c r="B17" t="n">
         <v>57740</v>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557902</v>
+        <v>557797</v>
       </c>
       <c r="R17" t="n">
-        <v>6977133</v>
+        <v>6977045</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130091903</v>
+        <v>130091924</v>
       </c>
       <c r="B18" t="n">
         <v>57740</v>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>557678</v>
+        <v>557902</v>
       </c>
       <c r="R18" t="n">
-        <v>6977236</v>
+        <v>6977133</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,7 +2379,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130091930</v>
+        <v>130091903</v>
       </c>
       <c r="B19" t="n">
         <v>57740</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557797</v>
+        <v>557678</v>
       </c>
       <c r="R19" t="n">
-        <v>6977045</v>
+        <v>6977236</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130091956</v>
+        <v>130091938</v>
       </c>
       <c r="B20" t="n">
-        <v>80194</v>
+        <v>57740</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557820</v>
+        <v>557679</v>
       </c>
       <c r="R20" t="n">
-        <v>6977049</v>
+        <v>6977111</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,6 +2552,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,10 +2583,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130091950</v>
+        <v>130091940</v>
       </c>
       <c r="B21" t="n">
-        <v>80194</v>
+        <v>57740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2594,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558152</v>
+        <v>557675</v>
       </c>
       <c r="R21" t="n">
-        <v>6977036</v>
+        <v>6977087</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,6 +2654,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Årsfärska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2675,7 +2685,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130091962</v>
+        <v>130091950</v>
       </c>
       <c r="B22" t="n">
         <v>80194</v>
@@ -2710,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557678</v>
+        <v>558152</v>
       </c>
       <c r="R22" t="n">
-        <v>6977026</v>
+        <v>6977036</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,10 +2782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130091940</v>
+        <v>130091962</v>
       </c>
       <c r="B23" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,21 +2793,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557675</v>
+        <v>557678</v>
       </c>
       <c r="R23" t="n">
-        <v>6977087</v>
+        <v>6977026</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2853,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Årsfärska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2874,10 +2879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130091938</v>
+        <v>130091956</v>
       </c>
       <c r="B24" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2890,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557679</v>
+        <v>557820</v>
       </c>
       <c r="R24" t="n">
-        <v>6977111</v>
+        <v>6977049</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,11 +2950,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,7 +2976,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130091932</v>
+        <v>130091897</v>
       </c>
       <c r="B25" t="n">
         <v>57740</v>
@@ -3005,16 +3005,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557737</v>
+        <v>557596</v>
       </c>
       <c r="R25" t="n">
-        <v>6977023</v>
+        <v>6977180</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,7 +3059,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Gammalt bohål i grantickerötad högstubbe. Bohålets diameter är omkring 4,5-5 cm. Hålet sitter omkring  en meter ovan mark. I högstubben, som kanske är fem meter hög, finns omkring 4,5 fler påbörjade bohål.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,7 +3086,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130091901</v>
+        <v>130091932</v>
       </c>
       <c r="B26" t="n">
         <v>57740</v>
@@ -3113,10 +3121,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557649</v>
+        <v>557737</v>
       </c>
       <c r="R26" t="n">
-        <v>6977216</v>
+        <v>6977023</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3153,7 +3161,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3180,7 +3188,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130091897</v>
+        <v>130091901</v>
       </c>
       <c r="B27" t="n">
         <v>57740</v>
@@ -3209,24 +3217,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557596</v>
+        <v>557649</v>
       </c>
       <c r="R27" t="n">
-        <v>6977180</v>
+        <v>6977216</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Gammalt bohål i grantickerötad högstubbe. Bohålets diameter är omkring 4,5-5 cm. Hålet sitter omkring  en meter ovan mark. I högstubben, som kanske är fem meter hög, finns omkring 4,5 fler påbörjade bohål.</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3290,7 +3290,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130091929</v>
+        <v>130091927</v>
       </c>
       <c r="B28" t="n">
         <v>57740</v>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557813</v>
+        <v>557821</v>
       </c>
       <c r="R28" t="n">
-        <v>6977043</v>
+        <v>6977051</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Kommer lite kåda ur några hål varför jag rapporterar dem som färska.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3494,7 +3494,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130091905</v>
+        <v>130091929</v>
       </c>
       <c r="B30" t="n">
         <v>57740</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558162</v>
+        <v>557813</v>
       </c>
       <c r="R30" t="n">
-        <v>6977113</v>
+        <v>6977043</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall. Kommer lite kåda ur några hål varför jag rapporterar dem som färska.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3596,7 +3596,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130091927</v>
+        <v>130091899</v>
       </c>
       <c r="B31" t="n">
         <v>57740</v>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557821</v>
+        <v>557634</v>
       </c>
       <c r="R31" t="n">
-        <v>6977051</v>
+        <v>6977186</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3698,7 +3698,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130091899</v>
+        <v>130091905</v>
       </c>
       <c r="B32" t="n">
         <v>57740</v>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557634</v>
+        <v>558162</v>
       </c>
       <c r="R32" t="n">
-        <v>6977186</v>
+        <v>6977113</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3800,10 +3800,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130091919</v>
+        <v>130091970</v>
       </c>
       <c r="B33" t="n">
-        <v>57740</v>
+        <v>91643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3811,23 +3811,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3835,10 +3831,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558105</v>
+        <v>557600</v>
       </c>
       <c r="R33" t="n">
-        <v>6977169</v>
+        <v>6977180</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3871,11 +3867,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3902,10 +3893,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130091915</v>
+        <v>130091955</v>
       </c>
       <c r="B34" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3913,21 +3904,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3937,10 +3928,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558130</v>
+        <v>557821</v>
       </c>
       <c r="R34" t="n">
-        <v>6977157</v>
+        <v>6977051</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,11 +3964,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4106,10 +4092,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130091970</v>
+        <v>130091898</v>
       </c>
       <c r="B36" t="n">
-        <v>91643</v>
+        <v>57740</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4117,19 +4103,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4137,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557600</v>
+        <v>557607</v>
       </c>
       <c r="R36" t="n">
-        <v>6977180</v>
+        <v>6977172</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4173,6 +4163,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4199,10 +4194,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130091955</v>
+        <v>130091919</v>
       </c>
       <c r="B37" t="n">
-        <v>80194</v>
+        <v>57740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4210,21 +4205,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4234,10 +4229,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557821</v>
+        <v>558105</v>
       </c>
       <c r="R37" t="n">
-        <v>6977051</v>
+        <v>6977169</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4270,6 +4265,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4296,7 +4296,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130091898</v>
+        <v>130091915</v>
       </c>
       <c r="B38" t="n">
         <v>57740</v>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557607</v>
+        <v>558130</v>
       </c>
       <c r="R38" t="n">
-        <v>6977172</v>
+        <v>6977157</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4398,10 +4398,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130091925</v>
+        <v>130091895</v>
       </c>
       <c r="B39" t="n">
-        <v>57740</v>
+        <v>91623</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557904</v>
+        <v>557656</v>
       </c>
       <c r="R39" t="n">
-        <v>6977140</v>
+        <v>6977218</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4469,11 +4469,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4500,10 +4495,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130091942</v>
+        <v>130091896</v>
       </c>
       <c r="B40" t="n">
-        <v>80195</v>
+        <v>91623</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4511,21 +4506,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4535,10 +4530,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557679</v>
+        <v>557915</v>
       </c>
       <c r="R40" t="n">
-        <v>6977024</v>
+        <v>6977133</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4597,10 +4592,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130091907</v>
+        <v>130091942</v>
       </c>
       <c r="B41" t="n">
-        <v>57740</v>
+        <v>80195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4608,21 +4603,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4632,10 +4627,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558144</v>
+        <v>557679</v>
       </c>
       <c r="R41" t="n">
-        <v>6977042</v>
+        <v>6977024</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4668,11 +4663,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4699,10 +4689,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130091895</v>
+        <v>130091907</v>
       </c>
       <c r="B42" t="n">
-        <v>91623</v>
+        <v>57740</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4710,21 +4700,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4734,10 +4724,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557656</v>
+        <v>558144</v>
       </c>
       <c r="R42" t="n">
-        <v>6977218</v>
+        <v>6977042</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4770,6 +4760,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4796,10 +4791,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130091896</v>
+        <v>130091925</v>
       </c>
       <c r="B43" t="n">
-        <v>91623</v>
+        <v>57740</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4807,21 +4802,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4831,10 +4826,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557915</v>
+        <v>557904</v>
       </c>
       <c r="R43" t="n">
-        <v>6977133</v>
+        <v>6977140</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,6 +4862,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4893,32 +4893,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130091966</v>
+        <v>130091949</v>
       </c>
       <c r="B44" t="n">
-        <v>80230</v>
+        <v>80194</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557775</v>
+        <v>558142</v>
       </c>
       <c r="R44" t="n">
-        <v>6977068</v>
+        <v>6977034</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4990,32 +4990,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130091949</v>
+        <v>130091966</v>
       </c>
       <c r="B45" t="n">
-        <v>80194</v>
+        <v>80230</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558142</v>
+        <v>557775</v>
       </c>
       <c r="R45" t="n">
-        <v>6977034</v>
+        <v>6977068</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5291,10 +5291,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130091912</v>
+        <v>130091974</v>
       </c>
       <c r="B48" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5302,21 +5302,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5326,10 +5326,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558132</v>
+        <v>557715</v>
       </c>
       <c r="R48" t="n">
-        <v>6977158</v>
+        <v>6977026</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5362,11 +5362,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5393,10 +5388,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130091974</v>
+        <v>130091912</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>57740</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5404,21 +5399,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5428,10 +5423,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557715</v>
+        <v>558132</v>
       </c>
       <c r="R49" t="n">
-        <v>6977026</v>
+        <v>6977158</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5464,6 +5459,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5786,10 +5786,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130091928</v>
+        <v>130091968</v>
       </c>
       <c r="B53" t="n">
-        <v>57740</v>
+        <v>91619</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5797,21 +5797,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557821</v>
+        <v>557647</v>
       </c>
       <c r="R53" t="n">
-        <v>6977048</v>
+        <v>6977216</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5857,11 +5857,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6092,10 +6087,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130091947</v>
+        <v>130091928</v>
       </c>
       <c r="B56" t="n">
-        <v>80194</v>
+        <v>57740</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6103,21 +6098,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6127,10 +6122,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558180</v>
+        <v>557821</v>
       </c>
       <c r="R56" t="n">
-        <v>6977031</v>
+        <v>6977048</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6167,7 +6162,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6194,10 +6189,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130091968</v>
+        <v>130091947</v>
       </c>
       <c r="B57" t="n">
-        <v>91619</v>
+        <v>80194</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6205,21 +6200,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6229,10 +6224,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557647</v>
+        <v>558180</v>
       </c>
       <c r="R57" t="n">
-        <v>6977216</v>
+        <v>6977031</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6265,6 +6260,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6388,10 +6388,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130091961</v>
+        <v>130091923</v>
       </c>
       <c r="B59" t="n">
-        <v>80194</v>
+        <v>57740</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6399,21 +6399,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557676</v>
+        <v>557985</v>
       </c>
       <c r="R59" t="n">
-        <v>6977046</v>
+        <v>6977074</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6459,6 +6459,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6679,10 +6684,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130091923</v>
+        <v>130091961</v>
       </c>
       <c r="B62" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6690,21 +6695,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6714,10 +6719,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>557985</v>
+        <v>557676</v>
       </c>
       <c r="R62" t="n">
-        <v>6977074</v>
+        <v>6977046</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6750,11 +6755,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6781,10 +6781,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130091971</v>
+        <v>130091953</v>
       </c>
       <c r="B63" t="n">
-        <v>91643</v>
+        <v>80194</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6792,19 +6792,23 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6812,10 +6816,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>557796</v>
+        <v>557806</v>
       </c>
       <c r="R63" t="n">
-        <v>6977175</v>
+        <v>6977127</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,32 +6878,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130091931</v>
+        <v>130091965</v>
       </c>
       <c r="B64" t="n">
-        <v>57740</v>
+        <v>80230</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6909,10 +6913,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>557736</v>
+        <v>557684</v>
       </c>
       <c r="R64" t="n">
-        <v>6977135</v>
+        <v>6977076</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6945,11 +6949,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6976,10 +6975,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130091953</v>
+        <v>130091931</v>
       </c>
       <c r="B65" t="n">
-        <v>80194</v>
+        <v>57740</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6987,21 +6986,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7011,10 +7010,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557806</v>
+        <v>557736</v>
       </c>
       <c r="R65" t="n">
-        <v>6977127</v>
+        <v>6977135</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7047,6 +7046,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7073,34 +7077,30 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130091965</v>
+        <v>130091971</v>
       </c>
       <c r="B66" t="n">
-        <v>80230</v>
+        <v>91643</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7108,10 +7108,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557684</v>
+        <v>557796</v>
       </c>
       <c r="R66" t="n">
-        <v>6977076</v>
+        <v>6977175</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7170,30 +7170,34 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130091969</v>
+        <v>130091943</v>
       </c>
       <c r="B67" t="n">
-        <v>91643</v>
+        <v>92076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7201,10 +7205,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557703</v>
+        <v>557913</v>
       </c>
       <c r="R67" t="n">
-        <v>6977166</v>
+        <v>6977135</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7263,10 +7267,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130091951</v>
+        <v>130091969</v>
       </c>
       <c r="B68" t="n">
-        <v>80194</v>
+        <v>91643</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7274,23 +7278,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558055</v>
+        <v>557703</v>
       </c>
       <c r="R68" t="n">
-        <v>6977160</v>
+        <v>6977166</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7360,10 +7360,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130091908</v>
+        <v>130091951</v>
       </c>
       <c r="B69" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7371,21 +7371,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558158</v>
+        <v>558055</v>
       </c>
       <c r="R69" t="n">
-        <v>6977109</v>
+        <v>6977160</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7431,11 +7431,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7462,32 +7457,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130091943</v>
+        <v>130091908</v>
       </c>
       <c r="B70" t="n">
-        <v>92076</v>
+        <v>57740</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7497,10 +7492,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>557913</v>
+        <v>558158</v>
       </c>
       <c r="R70" t="n">
-        <v>6977135</v>
+        <v>6977109</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7533,6 +7528,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7661,10 +7661,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130091957</v>
+        <v>130091920</v>
       </c>
       <c r="B72" t="n">
-        <v>80194</v>
+        <v>57740</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7672,21 +7672,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>557818</v>
+        <v>558063</v>
       </c>
       <c r="R72" t="n">
-        <v>6977041</v>
+        <v>6977173</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7732,6 +7732,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7758,7 +7763,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130091920</v>
+        <v>130091902</v>
       </c>
       <c r="B73" t="n">
         <v>57740</v>
@@ -7793,10 +7798,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558063</v>
+        <v>557666</v>
       </c>
       <c r="R73" t="n">
-        <v>6977173</v>
+        <v>6977240</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7860,10 +7865,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130091902</v>
+        <v>130091957</v>
       </c>
       <c r="B74" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7871,21 +7876,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7895,10 +7900,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>557666</v>
+        <v>557818</v>
       </c>
       <c r="R74" t="n">
-        <v>6977240</v>
+        <v>6977041</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7931,11 +7936,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7962,32 +7962,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130091944</v>
+        <v>130091963</v>
       </c>
       <c r="B75" t="n">
-        <v>91921</v>
+        <v>80230</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7997,10 +7997,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557705</v>
+        <v>558184</v>
       </c>
       <c r="R75" t="n">
-        <v>6977169</v>
+        <v>6977035</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8059,32 +8059,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130091963</v>
+        <v>130091944</v>
       </c>
       <c r="B76" t="n">
-        <v>80230</v>
+        <v>91921</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558184</v>
+        <v>557705</v>
       </c>
       <c r="R76" t="n">
-        <v>6977035</v>
+        <v>6977169</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>

--- a/artfynd/A 57458-2025 artfynd.xlsx
+++ b/artfynd/A 57458-2025 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130091960</v>
+        <v>130091922</v>
       </c>
       <c r="B6" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557676</v>
+        <v>558032</v>
       </c>
       <c r="R6" t="n">
-        <v>6977079</v>
+        <v>6977158</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,7 +1175,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130091922</v>
+        <v>130091926</v>
       </c>
       <c r="B7" t="n">
         <v>57741</v>
@@ -1205,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558032</v>
+        <v>557842</v>
       </c>
       <c r="R7" t="n">
-        <v>6977158</v>
+        <v>6977126</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130091926</v>
+        <v>130091909</v>
       </c>
       <c r="B8" t="n">
         <v>57741</v>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557842</v>
+        <v>558154</v>
       </c>
       <c r="R8" t="n">
-        <v>6977126</v>
+        <v>6977116</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130091909</v>
+        <v>130091904</v>
       </c>
       <c r="B9" t="n">
         <v>57741</v>
@@ -1409,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558154</v>
+        <v>557758</v>
       </c>
       <c r="R9" t="n">
-        <v>6977116</v>
+        <v>6977187</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130091904</v>
+        <v>130091960</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557758</v>
+        <v>557676</v>
       </c>
       <c r="R10" t="n">
-        <v>6977187</v>
+        <v>6977079</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1552,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2578,7 +2578,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130091962</v>
+        <v>130091956</v>
       </c>
       <c r="B21" t="n">
         <v>80200</v>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557678</v>
+        <v>557820</v>
       </c>
       <c r="R21" t="n">
-        <v>6977026</v>
+        <v>6977049</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130091956</v>
+        <v>130091938</v>
       </c>
       <c r="B22" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557820</v>
+        <v>557679</v>
       </c>
       <c r="R22" t="n">
-        <v>6977049</v>
+        <v>6977111</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,6 +2746,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2772,7 +2777,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130091938</v>
+        <v>130091940</v>
       </c>
       <c r="B23" t="n">
         <v>57741</v>
@@ -2807,10 +2812,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557679</v>
+        <v>557675</v>
       </c>
       <c r="R23" t="n">
-        <v>6977111</v>
+        <v>6977087</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2847,7 +2852,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på gran. Årsfärska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2874,10 +2879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130091940</v>
+        <v>130091962</v>
       </c>
       <c r="B24" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2890,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557675</v>
+        <v>557678</v>
       </c>
       <c r="R24" t="n">
-        <v>6977087</v>
+        <v>6977026</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,11 +2950,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Årsfärska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3800,10 +3800,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130091955</v>
+        <v>130091919</v>
       </c>
       <c r="B33" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3811,21 +3811,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557821</v>
+        <v>558105</v>
       </c>
       <c r="R33" t="n">
-        <v>6977051</v>
+        <v>6977169</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3871,6 +3871,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3897,10 +3902,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130091970</v>
+        <v>130091915</v>
       </c>
       <c r="B34" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3908,19 +3913,23 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3928,10 +3937,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>557600</v>
+        <v>558130</v>
       </c>
       <c r="R34" t="n">
-        <v>6977180</v>
+        <v>6977157</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3964,6 +3973,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3990,10 +4004,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130091913</v>
+        <v>130091955</v>
       </c>
       <c r="B35" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4001,21 +4015,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4025,10 +4039,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558131</v>
+        <v>557821</v>
       </c>
       <c r="R35" t="n">
-        <v>6977156</v>
+        <v>6977051</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4061,11 +4075,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4092,10 +4101,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130091898</v>
+        <v>130091970</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>91659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4103,23 +4112,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4127,10 +4132,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557607</v>
+        <v>557600</v>
       </c>
       <c r="R36" t="n">
-        <v>6977172</v>
+        <v>6977180</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4163,11 +4168,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4194,7 +4194,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130091919</v>
+        <v>130091913</v>
       </c>
       <c r="B37" t="n">
         <v>57741</v>
@@ -4229,10 +4229,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558105</v>
+        <v>558131</v>
       </c>
       <c r="R37" t="n">
-        <v>6977169</v>
+        <v>6977156</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4296,7 +4296,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130091915</v>
+        <v>130091898</v>
       </c>
       <c r="B38" t="n">
         <v>57741</v>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558130</v>
+        <v>557607</v>
       </c>
       <c r="R38" t="n">
-        <v>6977157</v>
+        <v>6977172</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5291,10 +5291,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130091974</v>
+        <v>130091912</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5302,21 +5302,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5326,10 +5326,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557715</v>
+        <v>558132</v>
       </c>
       <c r="R48" t="n">
-        <v>6977026</v>
+        <v>6977158</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5362,6 +5362,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5388,10 +5393,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130091912</v>
+        <v>130091974</v>
       </c>
       <c r="B49" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5399,21 +5404,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5423,10 +5428,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558132</v>
+        <v>557715</v>
       </c>
       <c r="R49" t="n">
-        <v>6977158</v>
+        <v>6977026</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5459,11 +5464,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6781,30 +6781,34 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130091971</v>
+        <v>130091965</v>
       </c>
       <c r="B63" t="n">
-        <v>91659</v>
+        <v>80236</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6812,10 +6816,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>557796</v>
+        <v>557684</v>
       </c>
       <c r="R63" t="n">
-        <v>6977175</v>
+        <v>6977076</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,32 +6878,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130091965</v>
+        <v>130091953</v>
       </c>
       <c r="B64" t="n">
-        <v>80236</v>
+        <v>80200</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6909,10 +6913,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>557684</v>
+        <v>557806</v>
       </c>
       <c r="R64" t="n">
-        <v>6977076</v>
+        <v>6977127</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,10 +6975,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130091953</v>
+        <v>130091931</v>
       </c>
       <c r="B65" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6982,21 +6986,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7006,10 +7010,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557806</v>
+        <v>557736</v>
       </c>
       <c r="R65" t="n">
-        <v>6977127</v>
+        <v>6977135</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7042,6 +7046,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7068,10 +7077,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130091931</v>
+        <v>130091971</v>
       </c>
       <c r="B66" t="n">
-        <v>57741</v>
+        <v>91659</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7079,23 +7088,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7103,10 +7108,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557736</v>
+        <v>557796</v>
       </c>
       <c r="R66" t="n">
-        <v>6977135</v>
+        <v>6977175</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7139,11 +7144,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7170,32 +7170,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130091943</v>
+        <v>130091908</v>
       </c>
       <c r="B67" t="n">
-        <v>92092</v>
+        <v>57741</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557913</v>
+        <v>558158</v>
       </c>
       <c r="R67" t="n">
-        <v>6977135</v>
+        <v>6977109</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7241,6 +7241,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7267,30 +7272,34 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130091969</v>
+        <v>130091943</v>
       </c>
       <c r="B68" t="n">
-        <v>91659</v>
+        <v>92092</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7298,10 +7307,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>557703</v>
+        <v>557913</v>
       </c>
       <c r="R68" t="n">
-        <v>6977166</v>
+        <v>6977135</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7360,10 +7369,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130091908</v>
+        <v>130091969</v>
       </c>
       <c r="B69" t="n">
-        <v>57741</v>
+        <v>91659</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7371,23 +7380,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7395,10 +7400,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558158</v>
+        <v>557703</v>
       </c>
       <c r="R69" t="n">
-        <v>6977109</v>
+        <v>6977166</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7431,11 +7436,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7661,10 +7661,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130091920</v>
+        <v>130091957</v>
       </c>
       <c r="B72" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7672,21 +7672,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558063</v>
+        <v>557818</v>
       </c>
       <c r="R72" t="n">
-        <v>6977173</v>
+        <v>6977041</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7732,11 +7732,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7763,7 +7758,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130091902</v>
+        <v>130091920</v>
       </c>
       <c r="B73" t="n">
         <v>57741</v>
@@ -7798,10 +7793,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>557666</v>
+        <v>558063</v>
       </c>
       <c r="R73" t="n">
-        <v>6977240</v>
+        <v>6977173</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7865,10 +7860,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130091957</v>
+        <v>130091902</v>
       </c>
       <c r="B74" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7876,21 +7871,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7900,10 +7895,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>557818</v>
+        <v>557666</v>
       </c>
       <c r="R74" t="n">
-        <v>6977041</v>
+        <v>6977240</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7936,6 +7931,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 57458-2025 artfynd.xlsx
+++ b/artfynd/A 57458-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130091975</v>
+        <v>130091945</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557681</v>
+        <v>557675</v>
       </c>
       <c r="R2" t="n">
-        <v>6977020</v>
+        <v>6977245</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130091945</v>
+        <v>130091975</v>
       </c>
       <c r="B3" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557675</v>
+        <v>557681</v>
       </c>
       <c r="R3" t="n">
-        <v>6977245</v>
+        <v>6977020</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2578,7 +2578,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130091956</v>
+        <v>130091962</v>
       </c>
       <c r="B21" t="n">
         <v>80200</v>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557820</v>
+        <v>557678</v>
       </c>
       <c r="R21" t="n">
-        <v>6977049</v>
+        <v>6977026</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130091938</v>
+        <v>130091956</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557679</v>
+        <v>557820</v>
       </c>
       <c r="R22" t="n">
-        <v>6977111</v>
+        <v>6977049</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,11 +2746,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2777,7 +2772,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130091940</v>
+        <v>130091938</v>
       </c>
       <c r="B23" t="n">
         <v>57741</v>
@@ -2812,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557675</v>
+        <v>557679</v>
       </c>
       <c r="R23" t="n">
-        <v>6977087</v>
+        <v>6977111</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2852,7 +2847,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran. Årsfärska</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2879,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130091962</v>
+        <v>130091940</v>
       </c>
       <c r="B24" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,21 +2885,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557678</v>
+        <v>557675</v>
       </c>
       <c r="R24" t="n">
-        <v>6977026</v>
+        <v>6977087</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2950,6 +2945,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Årsfärska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3800,10 +3800,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130091919</v>
+        <v>130091955</v>
       </c>
       <c r="B33" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3811,21 +3811,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558105</v>
+        <v>557821</v>
       </c>
       <c r="R33" t="n">
-        <v>6977169</v>
+        <v>6977051</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3871,11 +3871,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3902,10 +3897,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130091915</v>
+        <v>130091970</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>91659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3913,23 +3908,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3937,10 +3928,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558130</v>
+        <v>557600</v>
       </c>
       <c r="R34" t="n">
-        <v>6977157</v>
+        <v>6977180</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,11 +3964,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4004,10 +3990,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130091955</v>
+        <v>130091913</v>
       </c>
       <c r="B35" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4015,21 +4001,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4039,10 +4025,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557821</v>
+        <v>558131</v>
       </c>
       <c r="R35" t="n">
-        <v>6977051</v>
+        <v>6977156</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4075,6 +4061,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4101,10 +4092,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130091970</v>
+        <v>130091898</v>
       </c>
       <c r="B36" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4112,19 +4103,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4132,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557600</v>
+        <v>557607</v>
       </c>
       <c r="R36" t="n">
-        <v>6977180</v>
+        <v>6977172</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4168,6 +4163,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4194,7 +4194,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130091913</v>
+        <v>130091919</v>
       </c>
       <c r="B37" t="n">
         <v>57741</v>
@@ -4229,10 +4229,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558131</v>
+        <v>558105</v>
       </c>
       <c r="R37" t="n">
-        <v>6977156</v>
+        <v>6977169</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4296,7 +4296,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130091898</v>
+        <v>130091915</v>
       </c>
       <c r="B38" t="n">
         <v>57741</v>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557607</v>
+        <v>558130</v>
       </c>
       <c r="R38" t="n">
-        <v>6977172</v>
+        <v>6977157</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5786,10 +5786,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130091947</v>
+        <v>130091918</v>
       </c>
       <c r="B53" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5797,21 +5797,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558180</v>
+        <v>558109</v>
       </c>
       <c r="R53" t="n">
-        <v>6977031</v>
+        <v>6977170</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5888,10 +5888,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130091954</v>
+        <v>130091917</v>
       </c>
       <c r="B54" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5899,21 +5899,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557797</v>
+        <v>558129</v>
       </c>
       <c r="R54" t="n">
-        <v>6977073</v>
+        <v>6977165</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5959,6 +5959,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5985,7 +5990,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130091918</v>
+        <v>130091928</v>
       </c>
       <c r="B55" t="n">
         <v>57741</v>
@@ -6020,10 +6025,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558109</v>
+        <v>557821</v>
       </c>
       <c r="R55" t="n">
-        <v>6977170</v>
+        <v>6977048</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6087,10 +6092,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130091917</v>
+        <v>130091968</v>
       </c>
       <c r="B56" t="n">
-        <v>57741</v>
+        <v>91635</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6098,21 +6103,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6122,10 +6127,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558129</v>
+        <v>557647</v>
       </c>
       <c r="R56" t="n">
-        <v>6977165</v>
+        <v>6977216</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6158,11 +6163,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6189,10 +6189,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130091928</v>
+        <v>130091947</v>
       </c>
       <c r="B57" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6200,21 +6200,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557821</v>
+        <v>558180</v>
       </c>
       <c r="R57" t="n">
-        <v>6977048</v>
+        <v>6977031</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6291,10 +6291,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130091968</v>
+        <v>130091954</v>
       </c>
       <c r="B58" t="n">
-        <v>91635</v>
+        <v>80200</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557647</v>
+        <v>557797</v>
       </c>
       <c r="R58" t="n">
-        <v>6977216</v>
+        <v>6977073</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6781,34 +6781,30 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130091965</v>
+        <v>130091971</v>
       </c>
       <c r="B63" t="n">
-        <v>80236</v>
+        <v>91659</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6816,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>557684</v>
+        <v>557796</v>
       </c>
       <c r="R63" t="n">
-        <v>6977076</v>
+        <v>6977175</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6878,32 +6874,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130091953</v>
+        <v>130091965</v>
       </c>
       <c r="B64" t="n">
-        <v>80200</v>
+        <v>80236</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6913,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>557806</v>
+        <v>557684</v>
       </c>
       <c r="R64" t="n">
-        <v>6977127</v>
+        <v>6977076</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6975,10 +6971,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130091931</v>
+        <v>130091953</v>
       </c>
       <c r="B65" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6986,21 +6982,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7010,10 +7006,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557736</v>
+        <v>557806</v>
       </c>
       <c r="R65" t="n">
-        <v>6977135</v>
+        <v>6977127</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7046,11 +7042,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7077,10 +7068,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130091971</v>
+        <v>130091931</v>
       </c>
       <c r="B66" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7088,19 +7079,23 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7108,10 +7103,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557796</v>
+        <v>557736</v>
       </c>
       <c r="R66" t="n">
-        <v>6977175</v>
+        <v>6977135</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7144,6 +7139,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7170,32 +7170,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130091908</v>
+        <v>130091943</v>
       </c>
       <c r="B67" t="n">
-        <v>57741</v>
+        <v>92092</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558158</v>
+        <v>557913</v>
       </c>
       <c r="R67" t="n">
-        <v>6977109</v>
+        <v>6977135</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7241,11 +7241,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7272,34 +7267,30 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130091943</v>
+        <v>130091969</v>
       </c>
       <c r="B68" t="n">
-        <v>92092</v>
+        <v>91659</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7307,10 +7298,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>557913</v>
+        <v>557703</v>
       </c>
       <c r="R68" t="n">
-        <v>6977135</v>
+        <v>6977166</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7369,10 +7360,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130091969</v>
+        <v>130091908</v>
       </c>
       <c r="B69" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7380,19 +7371,23 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7400,10 +7395,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>557703</v>
+        <v>558158</v>
       </c>
       <c r="R69" t="n">
-        <v>6977166</v>
+        <v>6977109</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7436,6 +7431,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7661,10 +7661,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130091957</v>
+        <v>130091920</v>
       </c>
       <c r="B72" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7672,21 +7672,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>557818</v>
+        <v>558063</v>
       </c>
       <c r="R72" t="n">
-        <v>6977041</v>
+        <v>6977173</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7732,6 +7732,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7758,7 +7763,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130091920</v>
+        <v>130091902</v>
       </c>
       <c r="B73" t="n">
         <v>57741</v>
@@ -7793,10 +7798,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558063</v>
+        <v>557666</v>
       </c>
       <c r="R73" t="n">
-        <v>6977173</v>
+        <v>6977240</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7860,10 +7865,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130091902</v>
+        <v>130091957</v>
       </c>
       <c r="B74" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7871,21 +7876,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7895,10 +7900,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>557666</v>
+        <v>557818</v>
       </c>
       <c r="R74" t="n">
-        <v>6977240</v>
+        <v>6977041</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7931,11 +7936,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 57458-2025 artfynd.xlsx
+++ b/artfynd/A 57458-2025 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130091922</v>
+        <v>130091960</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558032</v>
+        <v>557676</v>
       </c>
       <c r="R6" t="n">
-        <v>6977158</v>
+        <v>6977079</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130091926</v>
+        <v>130091922</v>
       </c>
       <c r="B7" t="n">
         <v>57741</v>
@@ -1210,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557842</v>
+        <v>558032</v>
       </c>
       <c r="R7" t="n">
-        <v>6977126</v>
+        <v>6977158</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1272,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130091909</v>
+        <v>130091926</v>
       </c>
       <c r="B8" t="n">
         <v>57741</v>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558154</v>
+        <v>557842</v>
       </c>
       <c r="R8" t="n">
-        <v>6977116</v>
+        <v>6977126</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1347,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1374,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130091904</v>
+        <v>130091909</v>
       </c>
       <c r="B9" t="n">
         <v>57741</v>
@@ -1414,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557758</v>
+        <v>558154</v>
       </c>
       <c r="R9" t="n">
-        <v>6977187</v>
+        <v>6977116</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1449,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130091960</v>
+        <v>130091904</v>
       </c>
       <c r="B10" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557676</v>
+        <v>557758</v>
       </c>
       <c r="R10" t="n">
-        <v>6977079</v>
+        <v>6977187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -3086,7 +3086,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130091932</v>
+        <v>130091901</v>
       </c>
       <c r="B26" t="n">
         <v>57741</v>
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557737</v>
+        <v>557649</v>
       </c>
       <c r="R26" t="n">
-        <v>6977023</v>
+        <v>6977216</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3188,7 +3188,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130091901</v>
+        <v>130091932</v>
       </c>
       <c r="B27" t="n">
         <v>57741</v>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557649</v>
+        <v>557737</v>
       </c>
       <c r="R27" t="n">
-        <v>6977216</v>
+        <v>6977023</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3897,10 +3897,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130091970</v>
+        <v>130091913</v>
       </c>
       <c r="B34" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3908,19 +3908,23 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3928,10 +3932,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>557600</v>
+        <v>558131</v>
       </c>
       <c r="R34" t="n">
-        <v>6977180</v>
+        <v>6977156</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3964,6 +3968,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3990,7 +3999,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130091913</v>
+        <v>130091898</v>
       </c>
       <c r="B35" t="n">
         <v>57741</v>
@@ -4025,10 +4034,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558131</v>
+        <v>557607</v>
       </c>
       <c r="R35" t="n">
-        <v>6977156</v>
+        <v>6977172</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4065,7 +4074,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4092,7 +4101,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130091898</v>
+        <v>130091919</v>
       </c>
       <c r="B36" t="n">
         <v>57741</v>
@@ -4127,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557607</v>
+        <v>558105</v>
       </c>
       <c r="R36" t="n">
-        <v>6977172</v>
+        <v>6977169</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4167,7 +4176,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4194,7 +4203,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130091919</v>
+        <v>130091915</v>
       </c>
       <c r="B37" t="n">
         <v>57741</v>
@@ -4229,10 +4238,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558105</v>
+        <v>558130</v>
       </c>
       <c r="R37" t="n">
-        <v>6977169</v>
+        <v>6977157</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4296,10 +4305,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130091915</v>
+        <v>130091970</v>
       </c>
       <c r="B38" t="n">
-        <v>57741</v>
+        <v>91661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4307,23 +4316,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4331,10 +4336,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558130</v>
+        <v>557600</v>
       </c>
       <c r="R38" t="n">
-        <v>6977157</v>
+        <v>6977180</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4367,11 +4372,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4398,10 +4398,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130091895</v>
+        <v>130091925</v>
       </c>
       <c r="B39" t="n">
-        <v>91639</v>
+        <v>57741</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557656</v>
+        <v>557904</v>
       </c>
       <c r="R39" t="n">
-        <v>6977218</v>
+        <v>6977140</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4469,6 +4469,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4495,10 +4500,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130091896</v>
+        <v>130091895</v>
       </c>
       <c r="B40" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4530,10 +4535,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557915</v>
+        <v>557656</v>
       </c>
       <c r="R40" t="n">
-        <v>6977133</v>
+        <v>6977218</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4592,10 +4597,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130091942</v>
+        <v>130091896</v>
       </c>
       <c r="B41" t="n">
-        <v>80201</v>
+        <v>91641</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,21 +4608,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4627,10 +4632,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557679</v>
+        <v>557915</v>
       </c>
       <c r="R41" t="n">
-        <v>6977024</v>
+        <v>6977133</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,10 +4694,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130091907</v>
+        <v>130091942</v>
       </c>
       <c r="B42" t="n">
-        <v>57741</v>
+        <v>80201</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,21 +4705,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4724,10 +4729,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558144</v>
+        <v>557679</v>
       </c>
       <c r="R42" t="n">
-        <v>6977042</v>
+        <v>6977024</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4760,11 +4765,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4791,7 +4791,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130091925</v>
+        <v>130091907</v>
       </c>
       <c r="B43" t="n">
         <v>57741</v>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557904</v>
+        <v>558144</v>
       </c>
       <c r="R43" t="n">
-        <v>6977140</v>
+        <v>6977042</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4893,10 +4893,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130091949</v>
+        <v>130091939</v>
       </c>
       <c r="B44" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4904,21 +4904,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558142</v>
+        <v>557682</v>
       </c>
       <c r="R44" t="n">
-        <v>6977034</v>
+        <v>6977094</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,6 +4964,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4990,32 +4995,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130091966</v>
+        <v>130091949</v>
       </c>
       <c r="B45" t="n">
-        <v>80236</v>
+        <v>80200</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5025,10 +5030,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557775</v>
+        <v>558142</v>
       </c>
       <c r="R45" t="n">
-        <v>6977068</v>
+        <v>6977034</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5087,32 +5092,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130091921</v>
+        <v>130091966</v>
       </c>
       <c r="B46" t="n">
-        <v>57741</v>
+        <v>80236</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5122,10 +5127,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558051</v>
+        <v>557775</v>
       </c>
       <c r="R46" t="n">
-        <v>6977156</v>
+        <v>6977068</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,11 +5163,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5189,7 +5189,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130091939</v>
+        <v>130091921</v>
       </c>
       <c r="B47" t="n">
         <v>57741</v>
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557682</v>
+        <v>558051</v>
       </c>
       <c r="R47" t="n">
-        <v>6977094</v>
+        <v>6977156</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5291,10 +5291,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130091912</v>
+        <v>130091974</v>
       </c>
       <c r="B48" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5302,21 +5302,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5326,10 +5326,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558132</v>
+        <v>557715</v>
       </c>
       <c r="R48" t="n">
-        <v>6977158</v>
+        <v>6977026</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5362,11 +5362,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5393,10 +5388,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130091974</v>
+        <v>130091912</v>
       </c>
       <c r="B49" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5404,21 +5399,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5428,10 +5423,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557715</v>
+        <v>558132</v>
       </c>
       <c r="R49" t="n">
-        <v>6977026</v>
+        <v>6977158</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5464,6 +5459,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130091973</v>
+        <v>130091946</v>
       </c>
       <c r="B50" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557688</v>
+        <v>557850</v>
       </c>
       <c r="R50" t="n">
-        <v>6977239</v>
+        <v>6977174</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130091936</v>
+        <v>130091973</v>
       </c>
       <c r="B51" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5598,21 +5598,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557684</v>
+        <v>557688</v>
       </c>
       <c r="R51" t="n">
-        <v>6977104</v>
+        <v>6977239</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5658,11 +5658,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5689,10 +5684,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130091946</v>
+        <v>130091936</v>
       </c>
       <c r="B52" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5700,21 +5695,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5724,10 +5719,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557850</v>
+        <v>557684</v>
       </c>
       <c r="R52" t="n">
-        <v>6977174</v>
+        <v>6977104</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5760,6 +5755,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5786,10 +5786,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130091918</v>
+        <v>130091947</v>
       </c>
       <c r="B53" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5797,21 +5797,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558109</v>
+        <v>558180</v>
       </c>
       <c r="R53" t="n">
-        <v>6977170</v>
+        <v>6977031</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5888,10 +5888,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130091917</v>
+        <v>130091954</v>
       </c>
       <c r="B54" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5899,21 +5899,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558129</v>
+        <v>557797</v>
       </c>
       <c r="R54" t="n">
-        <v>6977165</v>
+        <v>6977073</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5959,11 +5959,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5990,10 +5985,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130091928</v>
+        <v>130091968</v>
       </c>
       <c r="B55" t="n">
-        <v>57741</v>
+        <v>91637</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6001,21 +5996,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6025,10 +6020,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557821</v>
+        <v>557647</v>
       </c>
       <c r="R55" t="n">
-        <v>6977048</v>
+        <v>6977216</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6061,11 +6056,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6092,10 +6082,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130091968</v>
+        <v>130091918</v>
       </c>
       <c r="B56" t="n">
-        <v>91635</v>
+        <v>57741</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6103,21 +6093,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6127,10 +6117,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>557647</v>
+        <v>558109</v>
       </c>
       <c r="R56" t="n">
-        <v>6977216</v>
+        <v>6977170</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6163,6 +6153,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6189,10 +6184,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130091947</v>
+        <v>130091917</v>
       </c>
       <c r="B57" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6200,21 +6195,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6224,10 +6219,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558180</v>
+        <v>558129</v>
       </c>
       <c r="R57" t="n">
-        <v>6977031</v>
+        <v>6977165</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6264,7 +6259,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6291,10 +6286,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130091954</v>
+        <v>130091928</v>
       </c>
       <c r="B58" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6302,21 +6297,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6326,10 +6321,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557797</v>
+        <v>557821</v>
       </c>
       <c r="R58" t="n">
-        <v>6977073</v>
+        <v>6977048</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6362,6 +6357,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6388,10 +6388,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130091923</v>
+        <v>130091961</v>
       </c>
       <c r="B59" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6399,21 +6399,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557985</v>
+        <v>557676</v>
       </c>
       <c r="R59" t="n">
-        <v>6977074</v>
+        <v>6977046</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6459,11 +6459,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6490,7 +6485,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130091961</v>
+        <v>130091948</v>
       </c>
       <c r="B60" t="n">
         <v>80200</v>
@@ -6525,10 +6520,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>557676</v>
+        <v>558157</v>
       </c>
       <c r="R60" t="n">
-        <v>6977046</v>
+        <v>6976991</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6587,32 +6582,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130091948</v>
+        <v>130091964</v>
       </c>
       <c r="B61" t="n">
-        <v>80200</v>
+        <v>80236</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6622,10 +6617,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558157</v>
+        <v>557819</v>
       </c>
       <c r="R61" t="n">
-        <v>6976991</v>
+        <v>6977050</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6684,32 +6679,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130091964</v>
+        <v>130091923</v>
       </c>
       <c r="B62" t="n">
-        <v>80236</v>
+        <v>57741</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6719,10 +6714,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>557819</v>
+        <v>557985</v>
       </c>
       <c r="R62" t="n">
-        <v>6977050</v>
+        <v>6977074</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6755,6 +6750,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6784,7 +6784,7 @@
         <v>130091971</v>
       </c>
       <c r="B63" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7170,32 +7170,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130091943</v>
+        <v>130091908</v>
       </c>
       <c r="B67" t="n">
-        <v>92092</v>
+        <v>57741</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557913</v>
+        <v>558158</v>
       </c>
       <c r="R67" t="n">
-        <v>6977135</v>
+        <v>6977109</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7241,6 +7241,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7267,10 +7272,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130091969</v>
+        <v>130091900</v>
       </c>
       <c r="B68" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7278,19 +7283,23 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7298,10 +7307,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>557703</v>
+        <v>557708</v>
       </c>
       <c r="R68" t="n">
-        <v>6977166</v>
+        <v>6977174</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7334,6 +7343,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7360,32 +7374,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130091908</v>
+        <v>130091943</v>
       </c>
       <c r="B69" t="n">
-        <v>57741</v>
+        <v>92094</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7395,10 +7409,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558158</v>
+        <v>557913</v>
       </c>
       <c r="R69" t="n">
-        <v>6977109</v>
+        <v>6977135</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7431,11 +7445,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7462,10 +7471,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130091900</v>
+        <v>130091951</v>
       </c>
       <c r="B70" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7473,21 +7482,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7497,10 +7506,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>557708</v>
+        <v>558055</v>
       </c>
       <c r="R70" t="n">
-        <v>6977174</v>
+        <v>6977160</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7533,11 +7542,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7564,10 +7568,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130091951</v>
+        <v>130091969</v>
       </c>
       <c r="B71" t="n">
-        <v>80200</v>
+        <v>91661</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7575,23 +7579,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558055</v>
+        <v>557703</v>
       </c>
       <c r="R71" t="n">
-        <v>6977160</v>
+        <v>6977166</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7962,32 +7962,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130091941</v>
+        <v>130091963</v>
       </c>
       <c r="B75" t="n">
-        <v>80201</v>
+        <v>80236</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7997,10 +7997,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557676</v>
+        <v>558184</v>
       </c>
       <c r="R75" t="n">
-        <v>6977043</v>
+        <v>6977035</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8059,10 +8059,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130091944</v>
+        <v>130091941</v>
       </c>
       <c r="B76" t="n">
-        <v>91937</v>
+        <v>80201</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>557705</v>
+        <v>557676</v>
       </c>
       <c r="R76" t="n">
-        <v>6977169</v>
+        <v>6977043</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8156,32 +8156,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130091963</v>
+        <v>130091944</v>
       </c>
       <c r="B77" t="n">
-        <v>80236</v>
+        <v>91939</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>558184</v>
+        <v>557705</v>
       </c>
       <c r="R77" t="n">
-        <v>6977035</v>
+        <v>6977169</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 57458-2025 artfynd.xlsx
+++ b/artfynd/A 57458-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130091945</v>
       </c>
       <c r="B2" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130091975</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130091906</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130091934</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130091960</v>
+        <v>130091922</v>
       </c>
       <c r="B6" t="n">
-        <v>80200</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557676</v>
+        <v>558032</v>
       </c>
       <c r="R6" t="n">
-        <v>6977079</v>
+        <v>6977158</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130091922</v>
+        <v>130091926</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558032</v>
+        <v>557842</v>
       </c>
       <c r="R7" t="n">
-        <v>6977158</v>
+        <v>6977126</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130091926</v>
+        <v>130091909</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557842</v>
+        <v>558154</v>
       </c>
       <c r="R8" t="n">
-        <v>6977126</v>
+        <v>6977116</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130091909</v>
+        <v>130091904</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558154</v>
+        <v>557758</v>
       </c>
       <c r="R9" t="n">
-        <v>6977116</v>
+        <v>6977187</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130091904</v>
+        <v>130091960</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>80285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557758</v>
+        <v>557676</v>
       </c>
       <c r="R10" t="n">
-        <v>6977187</v>
+        <v>6977079</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1552,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130091952</v>
+        <v>130091916</v>
       </c>
       <c r="B11" t="n">
-        <v>80200</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557819</v>
+        <v>558130</v>
       </c>
       <c r="R11" t="n">
-        <v>6977105</v>
+        <v>6977159</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,6 +1649,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1678,7 +1683,7 @@
         <v>130091959</v>
       </c>
       <c r="B12" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130091916</v>
+        <v>130091911</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558130</v>
+        <v>558143</v>
       </c>
       <c r="R13" t="n">
-        <v>6977159</v>
+        <v>6977143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,7 +1852,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1874,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130091911</v>
+        <v>130091952</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>80285</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558143</v>
+        <v>557819</v>
       </c>
       <c r="R14" t="n">
-        <v>6977143</v>
+        <v>6977105</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,11 +1950,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,32 +1976,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130091967</v>
+        <v>130091933</v>
       </c>
       <c r="B15" t="n">
-        <v>80236</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557677</v>
+        <v>557693</v>
       </c>
       <c r="R15" t="n">
-        <v>6977026</v>
+        <v>6977096</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,6 +2047,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2073,32 +2078,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130091933</v>
+        <v>130091967</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>80321</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2108,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557693</v>
+        <v>557677</v>
       </c>
       <c r="R16" t="n">
-        <v>6977096</v>
+        <v>6977026</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2144,11 +2149,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2178,7 +2178,7 @@
         <v>130091930</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>130091924</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>130091903</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130091950</v>
+        <v>130091938</v>
       </c>
       <c r="B20" t="n">
-        <v>80200</v>
+        <v>57826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558152</v>
+        <v>557679</v>
       </c>
       <c r="R20" t="n">
-        <v>6977036</v>
+        <v>6977111</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,6 +2552,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,10 +2583,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130091962</v>
+        <v>130091950</v>
       </c>
       <c r="B21" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2613,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557678</v>
+        <v>558152</v>
       </c>
       <c r="R21" t="n">
-        <v>6977026</v>
+        <v>6977036</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2680,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130091956</v>
+        <v>130091940</v>
       </c>
       <c r="B22" t="n">
-        <v>80200</v>
+        <v>57826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2691,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2715,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557820</v>
+        <v>557675</v>
       </c>
       <c r="R22" t="n">
-        <v>6977049</v>
+        <v>6977087</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,6 +2751,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Årsfärska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2772,10 +2782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130091938</v>
+        <v>130091962</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>80285</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,21 +2793,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557679</v>
+        <v>557678</v>
       </c>
       <c r="R23" t="n">
-        <v>6977111</v>
+        <v>6977026</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2853,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2874,10 +2879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130091940</v>
+        <v>130091956</v>
       </c>
       <c r="B24" t="n">
-        <v>57741</v>
+        <v>80285</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2890,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557675</v>
+        <v>557820</v>
       </c>
       <c r="R24" t="n">
-        <v>6977087</v>
+        <v>6977049</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,11 +2950,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Årsfärska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2979,7 +2979,7 @@
         <v>130091897</v>
       </c>
       <c r="B25" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130091901</v>
+        <v>130091932</v>
       </c>
       <c r="B26" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557649</v>
+        <v>557737</v>
       </c>
       <c r="R26" t="n">
-        <v>6977216</v>
+        <v>6977023</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3188,10 +3188,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130091932</v>
+        <v>130091901</v>
       </c>
       <c r="B27" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557737</v>
+        <v>557649</v>
       </c>
       <c r="R27" t="n">
-        <v>6977023</v>
+        <v>6977216</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3293,7 +3293,7 @@
         <v>130091927</v>
       </c>
       <c r="B28" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>130091910</v>
       </c>
       <c r="B29" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>130091929</v>
       </c>
       <c r="B30" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130091899</v>
+        <v>130091905</v>
       </c>
       <c r="B31" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557634</v>
+        <v>558162</v>
       </c>
       <c r="R31" t="n">
-        <v>6977186</v>
+        <v>6977113</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3698,10 +3698,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130091905</v>
+        <v>130091899</v>
       </c>
       <c r="B32" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558162</v>
+        <v>557634</v>
       </c>
       <c r="R32" t="n">
-        <v>6977113</v>
+        <v>6977186</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3800,10 +3800,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130091955</v>
+        <v>130091970</v>
       </c>
       <c r="B33" t="n">
-        <v>80200</v>
+        <v>91748</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3811,23 +3811,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3835,10 +3831,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557821</v>
+        <v>557600</v>
       </c>
       <c r="R33" t="n">
-        <v>6977051</v>
+        <v>6977180</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3897,10 +3893,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130091913</v>
+        <v>130091919</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3932,10 +3928,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558131</v>
+        <v>558105</v>
       </c>
       <c r="R34" t="n">
-        <v>6977156</v>
+        <v>6977169</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3999,10 +3995,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130091898</v>
+        <v>130091955</v>
       </c>
       <c r="B35" t="n">
-        <v>57741</v>
+        <v>80285</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4010,21 +4006,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4034,10 +4030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557607</v>
+        <v>557821</v>
       </c>
       <c r="R35" t="n">
-        <v>6977172</v>
+        <v>6977051</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4070,11 +4066,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4101,10 +4092,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130091919</v>
+        <v>130091913</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4136,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558105</v>
+        <v>558131</v>
       </c>
       <c r="R36" t="n">
-        <v>6977169</v>
+        <v>6977156</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4203,10 +4194,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130091915</v>
+        <v>130091898</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4238,10 +4229,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558130</v>
+        <v>557607</v>
       </c>
       <c r="R37" t="n">
-        <v>6977157</v>
+        <v>6977172</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4278,7 +4269,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4305,10 +4296,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130091970</v>
+        <v>130091915</v>
       </c>
       <c r="B38" t="n">
-        <v>91661</v>
+        <v>57826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4316,19 +4307,23 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4336,10 +4331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557600</v>
+        <v>558130</v>
       </c>
       <c r="R38" t="n">
-        <v>6977180</v>
+        <v>6977157</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4372,6 +4367,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4398,10 +4398,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130091925</v>
+        <v>130091895</v>
       </c>
       <c r="B39" t="n">
-        <v>57741</v>
+        <v>91728</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557904</v>
+        <v>557656</v>
       </c>
       <c r="R39" t="n">
-        <v>6977140</v>
+        <v>6977218</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4469,11 +4469,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4500,10 +4495,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130091895</v>
+        <v>130091907</v>
       </c>
       <c r="B40" t="n">
-        <v>91641</v>
+        <v>57826</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4511,21 +4506,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4535,10 +4530,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557656</v>
+        <v>558144</v>
       </c>
       <c r="R40" t="n">
-        <v>6977218</v>
+        <v>6977042</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4571,6 +4566,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4597,10 +4597,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130091896</v>
+        <v>130091925</v>
       </c>
       <c r="B41" t="n">
-        <v>91641</v>
+        <v>57826</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4608,21 +4608,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557915</v>
+        <v>557904</v>
       </c>
       <c r="R41" t="n">
-        <v>6977133</v>
+        <v>6977140</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4668,6 +4668,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4694,10 +4699,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130091942</v>
+        <v>130091896</v>
       </c>
       <c r="B42" t="n">
-        <v>80201</v>
+        <v>91728</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4705,21 +4710,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4729,10 +4734,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557679</v>
+        <v>557915</v>
       </c>
       <c r="R42" t="n">
-        <v>6977024</v>
+        <v>6977133</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,10 +4796,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130091907</v>
+        <v>130091942</v>
       </c>
       <c r="B43" t="n">
-        <v>57741</v>
+        <v>80286</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4802,21 +4807,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4826,10 +4831,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558144</v>
+        <v>557679</v>
       </c>
       <c r="R43" t="n">
-        <v>6977042</v>
+        <v>6977024</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4862,11 +4867,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4893,10 +4893,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130091939</v>
+        <v>130091949</v>
       </c>
       <c r="B44" t="n">
-        <v>57741</v>
+        <v>80285</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4904,21 +4904,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557682</v>
+        <v>558142</v>
       </c>
       <c r="R44" t="n">
-        <v>6977094</v>
+        <v>6977034</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,11 +4964,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4995,10 +4990,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130091949</v>
+        <v>130091921</v>
       </c>
       <c r="B45" t="n">
-        <v>80200</v>
+        <v>57826</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5006,21 +5001,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5030,10 +5025,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558142</v>
+        <v>558051</v>
       </c>
       <c r="R45" t="n">
-        <v>6977034</v>
+        <v>6977156</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5066,6 +5061,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5092,32 +5092,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130091966</v>
+        <v>130091939</v>
       </c>
       <c r="B46" t="n">
-        <v>80236</v>
+        <v>57826</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557775</v>
+        <v>557682</v>
       </c>
       <c r="R46" t="n">
-        <v>6977068</v>
+        <v>6977094</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5163,6 +5163,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5189,32 +5194,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130091921</v>
+        <v>130091966</v>
       </c>
       <c r="B47" t="n">
-        <v>57741</v>
+        <v>80321</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5224,10 +5229,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558051</v>
+        <v>557775</v>
       </c>
       <c r="R47" t="n">
-        <v>6977156</v>
+        <v>6977068</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,11 +5265,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5294,7 +5294,7 @@
         <v>130091974</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>130091912</v>
       </c>
       <c r="B49" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>130091946</v>
       </c>
       <c r="B50" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130091973</v>
+        <v>130091936</v>
       </c>
       <c r="B51" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5598,21 +5598,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557688</v>
+        <v>557684</v>
       </c>
       <c r="R51" t="n">
-        <v>6977239</v>
+        <v>6977104</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5658,6 +5658,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5684,10 +5689,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130091936</v>
+        <v>130091973</v>
       </c>
       <c r="B52" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5695,21 +5700,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5719,10 +5724,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557684</v>
+        <v>557688</v>
       </c>
       <c r="R52" t="n">
-        <v>6977104</v>
+        <v>6977239</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5755,11 +5760,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5789,7 +5789,7 @@
         <v>130091947</v>
       </c>
       <c r="B53" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5888,10 +5888,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130091954</v>
+        <v>130091918</v>
       </c>
       <c r="B54" t="n">
-        <v>80200</v>
+        <v>57826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5899,21 +5899,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557797</v>
+        <v>558109</v>
       </c>
       <c r="R54" t="n">
-        <v>6977073</v>
+        <v>6977170</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5959,6 +5959,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5985,10 +5990,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130091968</v>
+        <v>130091917</v>
       </c>
       <c r="B55" t="n">
-        <v>91637</v>
+        <v>57826</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5996,21 +6001,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6020,10 +6025,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557647</v>
+        <v>558129</v>
       </c>
       <c r="R55" t="n">
-        <v>6977216</v>
+        <v>6977165</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6056,6 +6061,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6082,10 +6092,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130091918</v>
+        <v>130091928</v>
       </c>
       <c r="B56" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6117,10 +6127,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558109</v>
+        <v>557821</v>
       </c>
       <c r="R56" t="n">
-        <v>6977170</v>
+        <v>6977048</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6184,10 +6194,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130091917</v>
+        <v>130091968</v>
       </c>
       <c r="B57" t="n">
-        <v>57741</v>
+        <v>91724</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6195,21 +6205,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6219,10 +6229,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558129</v>
+        <v>557647</v>
       </c>
       <c r="R57" t="n">
-        <v>6977165</v>
+        <v>6977216</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6255,11 +6265,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6286,10 +6291,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130091928</v>
+        <v>130091954</v>
       </c>
       <c r="B58" t="n">
-        <v>57741</v>
+        <v>80285</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6297,21 +6302,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6321,10 +6326,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557821</v>
+        <v>557797</v>
       </c>
       <c r="R58" t="n">
-        <v>6977048</v>
+        <v>6977073</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6357,11 +6362,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6388,10 +6388,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130091961</v>
+        <v>130091948</v>
       </c>
       <c r="B59" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557676</v>
+        <v>558157</v>
       </c>
       <c r="R59" t="n">
-        <v>6977046</v>
+        <v>6976991</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6485,10 +6485,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130091948</v>
+        <v>130091923</v>
       </c>
       <c r="B60" t="n">
-        <v>80200</v>
+        <v>57826</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6496,21 +6496,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558157</v>
+        <v>557985</v>
       </c>
       <c r="R60" t="n">
-        <v>6976991</v>
+        <v>6977074</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,6 +6556,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6585,7 +6590,7 @@
         <v>130091964</v>
       </c>
       <c r="B61" t="n">
-        <v>80236</v>
+        <v>80321</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6679,10 +6684,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130091923</v>
+        <v>130091961</v>
       </c>
       <c r="B62" t="n">
-        <v>57741</v>
+        <v>80285</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6690,21 +6695,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6714,10 +6719,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>557985</v>
+        <v>557676</v>
       </c>
       <c r="R62" t="n">
-        <v>6977074</v>
+        <v>6977046</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6750,11 +6755,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6781,10 +6781,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130091971</v>
+        <v>130091953</v>
       </c>
       <c r="B63" t="n">
-        <v>91661</v>
+        <v>80285</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6792,19 +6792,23 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6812,10 +6816,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>557796</v>
+        <v>557806</v>
       </c>
       <c r="R63" t="n">
-        <v>6977175</v>
+        <v>6977127</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,34 +6878,30 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130091965</v>
+        <v>130091971</v>
       </c>
       <c r="B64" t="n">
-        <v>80236</v>
+        <v>91748</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>557684</v>
+        <v>557796</v>
       </c>
       <c r="R64" t="n">
-        <v>6977076</v>
+        <v>6977175</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,10 +6971,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130091953</v>
+        <v>130091931</v>
       </c>
       <c r="B65" t="n">
-        <v>80200</v>
+        <v>57826</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6982,21 +6982,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557806</v>
+        <v>557736</v>
       </c>
       <c r="R65" t="n">
-        <v>6977127</v>
+        <v>6977135</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7042,6 +7042,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7068,32 +7073,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130091931</v>
+        <v>130091965</v>
       </c>
       <c r="B66" t="n">
-        <v>57741</v>
+        <v>80321</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7103,10 +7108,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557736</v>
+        <v>557684</v>
       </c>
       <c r="R66" t="n">
-        <v>6977135</v>
+        <v>6977076</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7139,11 +7144,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7170,32 +7170,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130091908</v>
+        <v>130091943</v>
       </c>
       <c r="B67" t="n">
-        <v>57741</v>
+        <v>92181</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558158</v>
+        <v>557913</v>
       </c>
       <c r="R67" t="n">
-        <v>6977109</v>
+        <v>6977135</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7241,11 +7241,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7272,10 +7267,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130091900</v>
+        <v>130091969</v>
       </c>
       <c r="B68" t="n">
-        <v>57741</v>
+        <v>91748</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7283,23 +7278,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7307,10 +7298,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>557708</v>
+        <v>557703</v>
       </c>
       <c r="R68" t="n">
-        <v>6977174</v>
+        <v>6977166</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7343,11 +7334,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7374,32 +7360,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130091943</v>
+        <v>130091908</v>
       </c>
       <c r="B69" t="n">
-        <v>92094</v>
+        <v>57826</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7409,10 +7395,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>557913</v>
+        <v>558158</v>
       </c>
       <c r="R69" t="n">
-        <v>6977135</v>
+        <v>6977109</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7445,6 +7431,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7471,10 +7462,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130091951</v>
+        <v>130091900</v>
       </c>
       <c r="B70" t="n">
-        <v>80200</v>
+        <v>57826</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7482,21 +7473,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7506,10 +7497,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558055</v>
+        <v>557708</v>
       </c>
       <c r="R70" t="n">
-        <v>6977160</v>
+        <v>6977174</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7542,6 +7533,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7568,10 +7564,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130091969</v>
+        <v>130091951</v>
       </c>
       <c r="B71" t="n">
-        <v>91661</v>
+        <v>80285</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7579,19 +7575,23 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>557703</v>
+        <v>558055</v>
       </c>
       <c r="R71" t="n">
-        <v>6977166</v>
+        <v>6977160</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7661,10 +7661,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130091920</v>
+        <v>130091957</v>
       </c>
       <c r="B72" t="n">
-        <v>57741</v>
+        <v>80285</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7672,21 +7672,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558063</v>
+        <v>557818</v>
       </c>
       <c r="R72" t="n">
-        <v>6977173</v>
+        <v>6977041</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7732,11 +7732,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7763,10 +7758,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130091902</v>
+        <v>130091920</v>
       </c>
       <c r="B73" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7798,10 +7793,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>557666</v>
+        <v>558063</v>
       </c>
       <c r="R73" t="n">
-        <v>6977240</v>
+        <v>6977173</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7865,10 +7860,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130091957</v>
+        <v>130091902</v>
       </c>
       <c r="B74" t="n">
-        <v>80200</v>
+        <v>57826</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7876,21 +7871,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7900,10 +7895,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>557818</v>
+        <v>557666</v>
       </c>
       <c r="R74" t="n">
-        <v>6977041</v>
+        <v>6977240</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7936,6 +7931,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7965,7 +7965,7 @@
         <v>130091963</v>
       </c>
       <c r="B75" t="n">
-        <v>80236</v>
+        <v>80321</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8059,10 +8059,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130091941</v>
+        <v>130091944</v>
       </c>
       <c r="B76" t="n">
-        <v>80201</v>
+        <v>92026</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>557676</v>
+        <v>557705</v>
       </c>
       <c r="R76" t="n">
-        <v>6977043</v>
+        <v>6977169</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8156,10 +8156,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130091944</v>
+        <v>130091941</v>
       </c>
       <c r="B77" t="n">
-        <v>91939</v>
+        <v>80286</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8167,21 +8167,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557705</v>
+        <v>557676</v>
       </c>
       <c r="R77" t="n">
-        <v>6977169</v>
+        <v>6977043</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 57458-2025 artfynd.xlsx
+++ b/artfynd/A 57458-2025 artfynd.xlsx
@@ -2976,7 +2976,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130091897</v>
+        <v>130091932</v>
       </c>
       <c r="B25" t="n">
         <v>57826</v>
@@ -3005,24 +3005,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557596</v>
+        <v>557737</v>
       </c>
       <c r="R25" t="n">
-        <v>6977180</v>
+        <v>6977023</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,7 +3051,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gammalt bohål i grantickerötad högstubbe. Bohålets diameter är omkring 4,5-5 cm. Hålet sitter omkring  en meter ovan mark. I högstubben, som kanske är fem meter hög, finns omkring 4,5 fler påbörjade bohål.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3086,7 +3078,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130091932</v>
+        <v>130091901</v>
       </c>
       <c r="B26" t="n">
         <v>57826</v>
@@ -3121,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557737</v>
+        <v>557649</v>
       </c>
       <c r="R26" t="n">
-        <v>6977023</v>
+        <v>6977216</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,7 +3153,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3188,7 +3180,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130091901</v>
+        <v>130091897</v>
       </c>
       <c r="B27" t="n">
         <v>57826</v>
@@ -3217,16 +3209,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557649</v>
+        <v>557596</v>
       </c>
       <c r="R27" t="n">
-        <v>6977216</v>
+        <v>6977180</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Gammalt bohål i grantickerötad högstubbe. Bohålets diameter är omkring 4,5-5 cm. Hålet sitter omkring  en meter ovan mark. I högstubben, som kanske är fem meter hög, finns omkring 4,5 fler påbörjade bohål.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 57458-2025 artfynd.xlsx
+++ b/artfynd/A 57458-2025 artfynd.xlsx
@@ -2976,7 +2976,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130091932</v>
+        <v>130091897</v>
       </c>
       <c r="B25" t="n">
         <v>57826</v>
@@ -3005,16 +3005,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557737</v>
+        <v>557596</v>
       </c>
       <c r="R25" t="n">
-        <v>6977023</v>
+        <v>6977180</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,7 +3059,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Gammalt bohål i grantickerötad högstubbe. Bohålets diameter är omkring 4,5-5 cm. Hålet sitter omkring  en meter ovan mark. I högstubben, som kanske är fem meter hög, finns omkring 4,5 fler påbörjade bohål.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,7 +3086,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130091901</v>
+        <v>130091932</v>
       </c>
       <c r="B26" t="n">
         <v>57826</v>
@@ -3113,10 +3121,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557649</v>
+        <v>557737</v>
       </c>
       <c r="R26" t="n">
-        <v>6977216</v>
+        <v>6977023</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3153,7 +3161,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3180,7 +3188,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130091897</v>
+        <v>130091901</v>
       </c>
       <c r="B27" t="n">
         <v>57826</v>
@@ -3209,24 +3217,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557596</v>
+        <v>557649</v>
       </c>
       <c r="R27" t="n">
-        <v>6977180</v>
+        <v>6977216</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Gammalt bohål i grantickerötad högstubbe. Bohålets diameter är omkring 4,5-5 cm. Hålet sitter omkring  en meter ovan mark. I högstubben, som kanske är fem meter hög, finns omkring 4,5 fler påbörjade bohål.</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -7170,32 +7170,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130091943</v>
+        <v>130091900</v>
       </c>
       <c r="B67" t="n">
-        <v>92181</v>
+        <v>57826</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557913</v>
+        <v>557708</v>
       </c>
       <c r="R67" t="n">
-        <v>6977135</v>
+        <v>6977174</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7241,6 +7241,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7267,10 +7272,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130091969</v>
+        <v>130091951</v>
       </c>
       <c r="B68" t="n">
-        <v>91748</v>
+        <v>80285</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7278,19 +7283,23 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7298,10 +7307,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>557703</v>
+        <v>558055</v>
       </c>
       <c r="R68" t="n">
-        <v>6977166</v>
+        <v>6977160</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7360,32 +7369,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130091908</v>
+        <v>130091943</v>
       </c>
       <c r="B69" t="n">
-        <v>57826</v>
+        <v>92181</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7395,10 +7404,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558158</v>
+        <v>557913</v>
       </c>
       <c r="R69" t="n">
-        <v>6977109</v>
+        <v>6977135</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7431,11 +7440,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7462,10 +7466,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130091900</v>
+        <v>130091969</v>
       </c>
       <c r="B70" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7473,23 +7477,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>557708</v>
+        <v>557703</v>
       </c>
       <c r="R70" t="n">
-        <v>6977174</v>
+        <v>6977166</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7533,11 +7533,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7564,10 +7559,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130091951</v>
+        <v>130091908</v>
       </c>
       <c r="B71" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7575,21 +7570,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7599,10 +7594,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558055</v>
+        <v>558158</v>
       </c>
       <c r="R71" t="n">
-        <v>6977160</v>
+        <v>6977109</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7635,6 +7630,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 57458-2025 artfynd.xlsx
+++ b/artfynd/A 57458-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130091945</v>
+        <v>130091975</v>
       </c>
       <c r="B2" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557675</v>
+        <v>557681</v>
       </c>
       <c r="R2" t="n">
-        <v>6977245</v>
+        <v>6977020</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130091975</v>
+        <v>130091945</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557681</v>
+        <v>557675</v>
       </c>
       <c r="R3" t="n">
-        <v>6977020</v>
+        <v>6977245</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130091922</v>
+        <v>130091960</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558032</v>
+        <v>557676</v>
       </c>
       <c r="R6" t="n">
-        <v>6977158</v>
+        <v>6977079</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130091926</v>
+        <v>130091922</v>
       </c>
       <c r="B7" t="n">
         <v>57826</v>
@@ -1210,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557842</v>
+        <v>558032</v>
       </c>
       <c r="R7" t="n">
-        <v>6977126</v>
+        <v>6977158</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1272,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130091909</v>
+        <v>130091926</v>
       </c>
       <c r="B8" t="n">
         <v>57826</v>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558154</v>
+        <v>557842</v>
       </c>
       <c r="R8" t="n">
-        <v>6977116</v>
+        <v>6977126</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1347,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1374,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130091904</v>
+        <v>130091909</v>
       </c>
       <c r="B9" t="n">
         <v>57826</v>
@@ -1414,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557758</v>
+        <v>558154</v>
       </c>
       <c r="R9" t="n">
-        <v>6977187</v>
+        <v>6977116</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1449,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130091960</v>
+        <v>130091904</v>
       </c>
       <c r="B10" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557676</v>
+        <v>557758</v>
       </c>
       <c r="R10" t="n">
-        <v>6977079</v>
+        <v>6977187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130091916</v>
+        <v>130091959</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558130</v>
+        <v>557704</v>
       </c>
       <c r="R11" t="n">
-        <v>6977159</v>
+        <v>6977024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,11 +1649,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,7 +1675,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130091959</v>
+        <v>130091952</v>
       </c>
       <c r="B12" t="n">
         <v>80285</v>
@@ -1715,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557704</v>
+        <v>557819</v>
       </c>
       <c r="R12" t="n">
-        <v>6977024</v>
+        <v>6977105</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,7 +1772,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130091911</v>
+        <v>130091916</v>
       </c>
       <c r="B13" t="n">
         <v>57826</v>
@@ -1812,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558143</v>
+        <v>558130</v>
       </c>
       <c r="R13" t="n">
-        <v>6977143</v>
+        <v>6977159</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,7 +1847,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130091952</v>
+        <v>130091911</v>
       </c>
       <c r="B14" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1885,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557819</v>
+        <v>558143</v>
       </c>
       <c r="R14" t="n">
-        <v>6977105</v>
+        <v>6977143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,6 +1945,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,32 +1976,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130091933</v>
+        <v>130091967</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>80321</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557693</v>
+        <v>557677</v>
       </c>
       <c r="R15" t="n">
-        <v>6977096</v>
+        <v>6977026</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,11 +2047,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,32 +2073,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130091967</v>
+        <v>130091933</v>
       </c>
       <c r="B16" t="n">
-        <v>80321</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557677</v>
+        <v>557693</v>
       </c>
       <c r="R16" t="n">
-        <v>6977026</v>
+        <v>6977096</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2149,6 +2144,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130091950</v>
+        <v>130091940</v>
       </c>
       <c r="B21" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558152</v>
+        <v>557675</v>
       </c>
       <c r="R21" t="n">
-        <v>6977036</v>
+        <v>6977087</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,6 +2654,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Årsfärska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2680,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130091940</v>
+        <v>130091950</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2691,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2715,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557675</v>
+        <v>558152</v>
       </c>
       <c r="R22" t="n">
-        <v>6977087</v>
+        <v>6977036</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2751,11 +2756,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Årsfärska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3596,7 +3596,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130091905</v>
+        <v>130091899</v>
       </c>
       <c r="B31" t="n">
         <v>57826</v>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558162</v>
+        <v>557634</v>
       </c>
       <c r="R31" t="n">
-        <v>6977113</v>
+        <v>6977186</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3698,7 +3698,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130091899</v>
+        <v>130091905</v>
       </c>
       <c r="B32" t="n">
         <v>57826</v>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557634</v>
+        <v>558162</v>
       </c>
       <c r="R32" t="n">
-        <v>6977186</v>
+        <v>6977113</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3800,10 +3800,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130091970</v>
+        <v>130091955</v>
       </c>
       <c r="B33" t="n">
-        <v>91748</v>
+        <v>80285</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3811,19 +3811,23 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3831,10 +3835,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557600</v>
+        <v>557821</v>
       </c>
       <c r="R33" t="n">
-        <v>6977180</v>
+        <v>6977051</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3893,7 +3897,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130091919</v>
+        <v>130091913</v>
       </c>
       <c r="B34" t="n">
         <v>57826</v>
@@ -3928,10 +3932,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558105</v>
+        <v>558131</v>
       </c>
       <c r="R34" t="n">
-        <v>6977169</v>
+        <v>6977156</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3995,10 +3999,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130091955</v>
+        <v>130091898</v>
       </c>
       <c r="B35" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4006,21 +4010,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4030,10 +4034,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557821</v>
+        <v>557607</v>
       </c>
       <c r="R35" t="n">
-        <v>6977051</v>
+        <v>6977172</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4066,6 +4070,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4092,7 +4101,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130091913</v>
+        <v>130091919</v>
       </c>
       <c r="B36" t="n">
         <v>57826</v>
@@ -4127,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558131</v>
+        <v>558105</v>
       </c>
       <c r="R36" t="n">
-        <v>6977156</v>
+        <v>6977169</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,7 +4203,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130091898</v>
+        <v>130091915</v>
       </c>
       <c r="B37" t="n">
         <v>57826</v>
@@ -4229,10 +4238,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557607</v>
+        <v>558130</v>
       </c>
       <c r="R37" t="n">
-        <v>6977172</v>
+        <v>6977157</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,7 +4278,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4296,10 +4305,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130091915</v>
+        <v>130091970</v>
       </c>
       <c r="B38" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4307,23 +4316,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4331,10 +4336,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558130</v>
+        <v>557600</v>
       </c>
       <c r="R38" t="n">
-        <v>6977157</v>
+        <v>6977180</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4367,11 +4372,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4495,10 +4495,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130091907</v>
+        <v>130091896</v>
       </c>
       <c r="B40" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4506,21 +4506,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558144</v>
+        <v>557915</v>
       </c>
       <c r="R40" t="n">
-        <v>6977042</v>
+        <v>6977133</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4566,11 +4566,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4597,10 +4592,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130091925</v>
+        <v>130091942</v>
       </c>
       <c r="B41" t="n">
-        <v>57826</v>
+        <v>80286</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4608,21 +4603,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4632,10 +4627,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557904</v>
+        <v>557679</v>
       </c>
       <c r="R41" t="n">
-        <v>6977140</v>
+        <v>6977024</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4668,11 +4663,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4699,10 +4689,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130091896</v>
+        <v>130091907</v>
       </c>
       <c r="B42" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4710,21 +4700,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4734,10 +4724,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557915</v>
+        <v>558144</v>
       </c>
       <c r="R42" t="n">
-        <v>6977133</v>
+        <v>6977042</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4770,6 +4760,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4796,10 +4791,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130091942</v>
+        <v>130091925</v>
       </c>
       <c r="B43" t="n">
-        <v>80286</v>
+        <v>57826</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4807,21 +4802,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4831,10 +4826,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557679</v>
+        <v>557904</v>
       </c>
       <c r="R43" t="n">
-        <v>6977024</v>
+        <v>6977140</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,6 +4862,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4893,10 +4893,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130091949</v>
+        <v>130091921</v>
       </c>
       <c r="B44" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4904,21 +4904,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558142</v>
+        <v>558051</v>
       </c>
       <c r="R44" t="n">
-        <v>6977034</v>
+        <v>6977156</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,6 +4964,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4990,7 +4995,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130091921</v>
+        <v>130091939</v>
       </c>
       <c r="B45" t="n">
         <v>57826</v>
@@ -5025,10 +5030,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558051</v>
+        <v>557682</v>
       </c>
       <c r="R45" t="n">
-        <v>6977156</v>
+        <v>6977094</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5065,7 +5070,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5092,10 +5097,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130091939</v>
+        <v>130091949</v>
       </c>
       <c r="B46" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5103,21 +5108,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5127,10 +5132,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557682</v>
+        <v>558142</v>
       </c>
       <c r="R46" t="n">
-        <v>6977094</v>
+        <v>6977034</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5163,11 +5168,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130091946</v>
+        <v>130091973</v>
       </c>
       <c r="B50" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557850</v>
+        <v>557688</v>
       </c>
       <c r="R50" t="n">
-        <v>6977174</v>
+        <v>6977239</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130091936</v>
+        <v>130091946</v>
       </c>
       <c r="B51" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5598,21 +5598,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557684</v>
+        <v>557850</v>
       </c>
       <c r="R51" t="n">
-        <v>6977104</v>
+        <v>6977174</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5658,11 +5658,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5689,10 +5684,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130091973</v>
+        <v>130091936</v>
       </c>
       <c r="B52" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5700,21 +5695,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5724,10 +5719,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557688</v>
+        <v>557684</v>
       </c>
       <c r="R52" t="n">
-        <v>6977239</v>
+        <v>6977104</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5760,6 +5755,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5888,10 +5888,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130091918</v>
+        <v>130091954</v>
       </c>
       <c r="B54" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5899,21 +5899,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558109</v>
+        <v>557797</v>
       </c>
       <c r="R54" t="n">
-        <v>6977170</v>
+        <v>6977073</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5959,11 +5959,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5990,7 +5985,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130091917</v>
+        <v>130091918</v>
       </c>
       <c r="B55" t="n">
         <v>57826</v>
@@ -6025,10 +6020,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558129</v>
+        <v>558109</v>
       </c>
       <c r="R55" t="n">
-        <v>6977165</v>
+        <v>6977170</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6092,7 +6087,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130091928</v>
+        <v>130091917</v>
       </c>
       <c r="B56" t="n">
         <v>57826</v>
@@ -6127,10 +6122,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>557821</v>
+        <v>558129</v>
       </c>
       <c r="R56" t="n">
-        <v>6977048</v>
+        <v>6977165</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6194,10 +6189,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130091968</v>
+        <v>130091928</v>
       </c>
       <c r="B57" t="n">
-        <v>91724</v>
+        <v>57826</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6205,21 +6200,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6229,10 +6224,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557647</v>
+        <v>557821</v>
       </c>
       <c r="R57" t="n">
-        <v>6977216</v>
+        <v>6977048</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6265,6 +6260,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6291,10 +6291,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130091954</v>
+        <v>130091968</v>
       </c>
       <c r="B58" t="n">
-        <v>80285</v>
+        <v>91724</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557797</v>
+        <v>557647</v>
       </c>
       <c r="R58" t="n">
-        <v>6977073</v>
+        <v>6977216</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6485,32 +6485,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130091923</v>
+        <v>130091964</v>
       </c>
       <c r="B60" t="n">
-        <v>57826</v>
+        <v>80321</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>557985</v>
+        <v>557819</v>
       </c>
       <c r="R60" t="n">
-        <v>6977074</v>
+        <v>6977050</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,11 +6556,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6587,32 +6582,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130091964</v>
+        <v>130091961</v>
       </c>
       <c r="B61" t="n">
-        <v>80321</v>
+        <v>80285</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6622,10 +6617,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>557819</v>
+        <v>557676</v>
       </c>
       <c r="R61" t="n">
-        <v>6977050</v>
+        <v>6977046</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6684,10 +6679,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130091961</v>
+        <v>130091923</v>
       </c>
       <c r="B62" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6695,21 +6690,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6719,10 +6714,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>557676</v>
+        <v>557985</v>
       </c>
       <c r="R62" t="n">
-        <v>6977046</v>
+        <v>6977074</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6755,6 +6750,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6878,30 +6878,34 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130091971</v>
+        <v>130091965</v>
       </c>
       <c r="B64" t="n">
-        <v>91748</v>
+        <v>80321</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -6909,10 +6913,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>557796</v>
+        <v>557684</v>
       </c>
       <c r="R64" t="n">
-        <v>6977175</v>
+        <v>6977076</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,10 +6975,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130091931</v>
+        <v>130091971</v>
       </c>
       <c r="B65" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6982,23 +6986,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557736</v>
+        <v>557796</v>
       </c>
       <c r="R65" t="n">
-        <v>6977135</v>
+        <v>6977175</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7042,11 +7042,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7073,32 +7068,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130091965</v>
+        <v>130091931</v>
       </c>
       <c r="B66" t="n">
-        <v>80321</v>
+        <v>57826</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7108,10 +7103,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557684</v>
+        <v>557736</v>
       </c>
       <c r="R66" t="n">
-        <v>6977076</v>
+        <v>6977135</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7144,6 +7139,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7170,32 +7170,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130091900</v>
+        <v>130091943</v>
       </c>
       <c r="B67" t="n">
-        <v>57826</v>
+        <v>92181</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557708</v>
+        <v>557913</v>
       </c>
       <c r="R67" t="n">
-        <v>6977174</v>
+        <v>6977135</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7241,11 +7241,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7369,34 +7364,30 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130091943</v>
+        <v>130091969</v>
       </c>
       <c r="B69" t="n">
-        <v>92181</v>
+        <v>91748</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7404,10 +7395,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>557913</v>
+        <v>557703</v>
       </c>
       <c r="R69" t="n">
-        <v>6977135</v>
+        <v>6977166</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7466,10 +7457,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130091969</v>
+        <v>130091908</v>
       </c>
       <c r="B70" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7477,19 +7468,23 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7497,10 +7492,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>557703</v>
+        <v>558158</v>
       </c>
       <c r="R70" t="n">
-        <v>6977166</v>
+        <v>6977109</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7533,6 +7528,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7559,7 +7559,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130091908</v>
+        <v>130091900</v>
       </c>
       <c r="B71" t="n">
         <v>57826</v>
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558158</v>
+        <v>557708</v>
       </c>
       <c r="R71" t="n">
-        <v>6977109</v>
+        <v>6977174</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7962,32 +7962,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130091963</v>
+        <v>130091944</v>
       </c>
       <c r="B75" t="n">
-        <v>80321</v>
+        <v>92026</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7997,10 +7997,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558184</v>
+        <v>557705</v>
       </c>
       <c r="R75" t="n">
-        <v>6977035</v>
+        <v>6977169</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8059,10 +8059,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130091944</v>
+        <v>130091941</v>
       </c>
       <c r="B76" t="n">
-        <v>92026</v>
+        <v>80286</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>557705</v>
+        <v>557676</v>
       </c>
       <c r="R76" t="n">
-        <v>6977169</v>
+        <v>6977043</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8156,32 +8156,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130091941</v>
+        <v>130091963</v>
       </c>
       <c r="B77" t="n">
-        <v>80286</v>
+        <v>80321</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557676</v>
+        <v>558184</v>
       </c>
       <c r="R77" t="n">
-        <v>6977043</v>
+        <v>6977035</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 57458-2025 artfynd.xlsx
+++ b/artfynd/A 57458-2025 artfynd.xlsx
@@ -1578,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130091959</v>
+        <v>130091916</v>
       </c>
       <c r="B11" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557704</v>
+        <v>558130</v>
       </c>
       <c r="R11" t="n">
-        <v>6977024</v>
+        <v>6977159</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,6 +1649,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130091952</v>
+        <v>130091911</v>
       </c>
       <c r="B12" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557819</v>
+        <v>558143</v>
       </c>
       <c r="R12" t="n">
-        <v>6977105</v>
+        <v>6977143</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,6 +1751,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1772,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130091916</v>
+        <v>130091959</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1807,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558130</v>
+        <v>557704</v>
       </c>
       <c r="R13" t="n">
-        <v>6977159</v>
+        <v>6977024</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,11 +1853,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1874,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130091911</v>
+        <v>130091952</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558143</v>
+        <v>557819</v>
       </c>
       <c r="R14" t="n">
-        <v>6977143</v>
+        <v>6977105</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,11 +1950,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2685,7 +2685,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130091950</v>
+        <v>130091956</v>
       </c>
       <c r="B22" t="n">
         <v>80285</v>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558152</v>
+        <v>557820</v>
       </c>
       <c r="R22" t="n">
-        <v>6977036</v>
+        <v>6977049</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130091962</v>
+        <v>130091950</v>
       </c>
       <c r="B23" t="n">
         <v>80285</v>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557678</v>
+        <v>558152</v>
       </c>
       <c r="R23" t="n">
-        <v>6977026</v>
+        <v>6977036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2879,7 +2879,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130091956</v>
+        <v>130091962</v>
       </c>
       <c r="B24" t="n">
         <v>80285</v>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557820</v>
+        <v>557678</v>
       </c>
       <c r="R24" t="n">
-        <v>6977049</v>
+        <v>6977026</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3897,10 +3897,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130091913</v>
+        <v>130091970</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3908,23 +3908,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3932,10 +3928,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558131</v>
+        <v>557600</v>
       </c>
       <c r="R34" t="n">
-        <v>6977156</v>
+        <v>6977180</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3968,11 +3964,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3999,7 +3990,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130091898</v>
+        <v>130091913</v>
       </c>
       <c r="B35" t="n">
         <v>57826</v>
@@ -4034,10 +4025,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557607</v>
+        <v>558131</v>
       </c>
       <c r="R35" t="n">
-        <v>6977172</v>
+        <v>6977156</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4074,7 +4065,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4101,7 +4092,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130091919</v>
+        <v>130091898</v>
       </c>
       <c r="B36" t="n">
         <v>57826</v>
@@ -4136,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558105</v>
+        <v>557607</v>
       </c>
       <c r="R36" t="n">
-        <v>6977169</v>
+        <v>6977172</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4176,7 +4167,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4203,7 +4194,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130091915</v>
+        <v>130091919</v>
       </c>
       <c r="B37" t="n">
         <v>57826</v>
@@ -4238,10 +4229,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558130</v>
+        <v>558105</v>
       </c>
       <c r="R37" t="n">
-        <v>6977157</v>
+        <v>6977169</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4305,10 +4296,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130091970</v>
+        <v>130091915</v>
       </c>
       <c r="B38" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4316,19 +4307,23 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4336,10 +4331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557600</v>
+        <v>558130</v>
       </c>
       <c r="R38" t="n">
-        <v>6977180</v>
+        <v>6977157</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4372,6 +4367,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4398,10 +4398,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130091895</v>
+        <v>130091942</v>
       </c>
       <c r="B39" t="n">
-        <v>91728</v>
+        <v>80286</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557656</v>
+        <v>557679</v>
       </c>
       <c r="R39" t="n">
-        <v>6977218</v>
+        <v>6977024</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4495,7 +4495,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130091896</v>
+        <v>130091895</v>
       </c>
       <c r="B40" t="n">
         <v>91728</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557915</v>
+        <v>557656</v>
       </c>
       <c r="R40" t="n">
-        <v>6977133</v>
+        <v>6977218</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4592,10 +4592,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130091942</v>
+        <v>130091896</v>
       </c>
       <c r="B41" t="n">
-        <v>80286</v>
+        <v>91728</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557679</v>
+        <v>557915</v>
       </c>
       <c r="R41" t="n">
-        <v>6977024</v>
+        <v>6977133</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4893,10 +4893,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130091921</v>
+        <v>130091949</v>
       </c>
       <c r="B44" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4904,21 +4904,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558051</v>
+        <v>558142</v>
       </c>
       <c r="R44" t="n">
-        <v>6977156</v>
+        <v>6977034</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,11 +4964,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4995,32 +4990,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130091939</v>
+        <v>130091966</v>
       </c>
       <c r="B45" t="n">
-        <v>57826</v>
+        <v>80321</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5030,10 +5025,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557682</v>
+        <v>557775</v>
       </c>
       <c r="R45" t="n">
-        <v>6977094</v>
+        <v>6977068</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5066,11 +5061,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5097,10 +5087,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130091949</v>
+        <v>130091921</v>
       </c>
       <c r="B46" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5108,21 +5098,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5132,10 +5122,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558142</v>
+        <v>558051</v>
       </c>
       <c r="R46" t="n">
-        <v>6977034</v>
+        <v>6977156</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5168,6 +5158,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5194,32 +5189,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130091966</v>
+        <v>130091939</v>
       </c>
       <c r="B47" t="n">
-        <v>80321</v>
+        <v>57826</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5229,10 +5224,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557775</v>
+        <v>557682</v>
       </c>
       <c r="R47" t="n">
-        <v>6977068</v>
+        <v>6977094</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5265,6 +5260,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5786,10 +5786,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130091947</v>
+        <v>130091968</v>
       </c>
       <c r="B53" t="n">
-        <v>80285</v>
+        <v>91724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5797,21 +5797,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558180</v>
+        <v>557647</v>
       </c>
       <c r="R53" t="n">
-        <v>6977031</v>
+        <v>6977216</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5857,11 +5857,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5888,7 +5883,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130091954</v>
+        <v>130091947</v>
       </c>
       <c r="B54" t="n">
         <v>80285</v>
@@ -5923,10 +5918,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557797</v>
+        <v>558180</v>
       </c>
       <c r="R54" t="n">
-        <v>6977073</v>
+        <v>6977031</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5959,6 +5954,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5985,10 +5985,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130091918</v>
+        <v>130091954</v>
       </c>
       <c r="B55" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5996,21 +5996,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6020,10 +6020,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558109</v>
+        <v>557797</v>
       </c>
       <c r="R55" t="n">
-        <v>6977170</v>
+        <v>6977073</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6056,11 +6056,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6087,7 +6082,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130091917</v>
+        <v>130091918</v>
       </c>
       <c r="B56" t="n">
         <v>57826</v>
@@ -6122,10 +6117,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558129</v>
+        <v>558109</v>
       </c>
       <c r="R56" t="n">
-        <v>6977165</v>
+        <v>6977170</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6189,7 +6184,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130091928</v>
+        <v>130091917</v>
       </c>
       <c r="B57" t="n">
         <v>57826</v>
@@ -6224,10 +6219,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557821</v>
+        <v>558129</v>
       </c>
       <c r="R57" t="n">
-        <v>6977048</v>
+        <v>6977165</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6291,10 +6286,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130091968</v>
+        <v>130091928</v>
       </c>
       <c r="B58" t="n">
-        <v>91724</v>
+        <v>57826</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6302,21 +6297,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6326,10 +6321,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557647</v>
+        <v>557821</v>
       </c>
       <c r="R58" t="n">
-        <v>6977216</v>
+        <v>6977048</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6362,6 +6357,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6781,10 +6781,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130091953</v>
+        <v>130091971</v>
       </c>
       <c r="B63" t="n">
-        <v>80285</v>
+        <v>91748</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6792,23 +6792,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6816,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>557806</v>
+        <v>557796</v>
       </c>
       <c r="R63" t="n">
-        <v>6977127</v>
+        <v>6977175</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6878,32 +6874,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130091965</v>
+        <v>130091931</v>
       </c>
       <c r="B64" t="n">
-        <v>80321</v>
+        <v>57826</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6913,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>557684</v>
+        <v>557736</v>
       </c>
       <c r="R64" t="n">
-        <v>6977076</v>
+        <v>6977135</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6949,6 +6945,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6975,10 +6976,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130091971</v>
+        <v>130091953</v>
       </c>
       <c r="B65" t="n">
-        <v>91748</v>
+        <v>80285</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6986,19 +6987,23 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7006,10 +7011,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557796</v>
+        <v>557806</v>
       </c>
       <c r="R65" t="n">
-        <v>6977175</v>
+        <v>6977127</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7068,32 +7073,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130091931</v>
+        <v>130091965</v>
       </c>
       <c r="B66" t="n">
-        <v>57826</v>
+        <v>80321</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7103,10 +7108,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557736</v>
+        <v>557684</v>
       </c>
       <c r="R66" t="n">
-        <v>6977135</v>
+        <v>6977076</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7139,11 +7144,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7267,10 +7267,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130091951</v>
+        <v>130091908</v>
       </c>
       <c r="B68" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7278,21 +7278,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7302,10 +7302,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558055</v>
+        <v>558158</v>
       </c>
       <c r="R68" t="n">
-        <v>6977160</v>
+        <v>6977109</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7338,6 +7338,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7364,10 +7369,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130091969</v>
+        <v>130091900</v>
       </c>
       <c r="B69" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7375,19 +7380,23 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7395,10 +7404,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>557703</v>
+        <v>557708</v>
       </c>
       <c r="R69" t="n">
-        <v>6977166</v>
+        <v>6977174</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7431,6 +7440,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7457,10 +7471,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130091908</v>
+        <v>130091969</v>
       </c>
       <c r="B70" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7468,23 +7482,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7492,10 +7502,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558158</v>
+        <v>557703</v>
       </c>
       <c r="R70" t="n">
-        <v>6977109</v>
+        <v>6977166</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7528,11 +7538,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7559,10 +7564,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130091900</v>
+        <v>130091951</v>
       </c>
       <c r="B71" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7570,21 +7575,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7594,10 +7599,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>557708</v>
+        <v>558055</v>
       </c>
       <c r="R71" t="n">
-        <v>6977174</v>
+        <v>6977160</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7630,11 +7635,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7962,32 +7962,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130091944</v>
+        <v>130091963</v>
       </c>
       <c r="B75" t="n">
-        <v>92026</v>
+        <v>80321</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7997,10 +7997,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557705</v>
+        <v>558184</v>
       </c>
       <c r="R75" t="n">
-        <v>6977169</v>
+        <v>6977035</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8059,10 +8059,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130091941</v>
+        <v>130091944</v>
       </c>
       <c r="B76" t="n">
-        <v>80286</v>
+        <v>92026</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>557676</v>
+        <v>557705</v>
       </c>
       <c r="R76" t="n">
-        <v>6977043</v>
+        <v>6977169</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8156,32 +8156,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130091963</v>
+        <v>130091941</v>
       </c>
       <c r="B77" t="n">
-        <v>80321</v>
+        <v>80286</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>558184</v>
+        <v>557676</v>
       </c>
       <c r="R77" t="n">
-        <v>6977035</v>
+        <v>6977043</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 57458-2025 artfynd.xlsx
+++ b/artfynd/A 57458-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130091975</v>
+        <v>130091945</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557681</v>
+        <v>557675</v>
       </c>
       <c r="R2" t="n">
-        <v>6977020</v>
+        <v>6977245</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130091945</v>
+        <v>130091975</v>
       </c>
       <c r="B3" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557675</v>
+        <v>557681</v>
       </c>
       <c r="R3" t="n">
-        <v>6977245</v>
+        <v>6977020</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130091916</v>
+        <v>130091959</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558130</v>
+        <v>557704</v>
       </c>
       <c r="R11" t="n">
-        <v>6977159</v>
+        <v>6977024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,11 +1649,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130091911</v>
+        <v>130091952</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558143</v>
+        <v>557819</v>
       </c>
       <c r="R12" t="n">
-        <v>6977143</v>
+        <v>6977105</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,11 +1746,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130091959</v>
+        <v>130091916</v>
       </c>
       <c r="B13" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557704</v>
+        <v>558130</v>
       </c>
       <c r="R13" t="n">
-        <v>6977024</v>
+        <v>6977159</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,6 +1843,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130091952</v>
+        <v>130091911</v>
       </c>
       <c r="B14" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1885,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557819</v>
+        <v>558143</v>
       </c>
       <c r="R14" t="n">
-        <v>6977105</v>
+        <v>6977143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,6 +1945,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130091938</v>
+        <v>130091950</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557679</v>
+        <v>558152</v>
       </c>
       <c r="R20" t="n">
-        <v>6977111</v>
+        <v>6977036</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,11 +2552,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130091940</v>
+        <v>130091962</v>
       </c>
       <c r="B21" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2594,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2618,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557675</v>
+        <v>557678</v>
       </c>
       <c r="R21" t="n">
-        <v>6977087</v>
+        <v>6977026</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,11 +2649,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Årsfärska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2782,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130091950</v>
+        <v>130091938</v>
       </c>
       <c r="B23" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2793,21 +2783,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558152</v>
+        <v>557679</v>
       </c>
       <c r="R23" t="n">
-        <v>6977036</v>
+        <v>6977111</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2853,6 +2843,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2879,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130091962</v>
+        <v>130091940</v>
       </c>
       <c r="B24" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,21 +2885,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557678</v>
+        <v>557675</v>
       </c>
       <c r="R24" t="n">
-        <v>6977026</v>
+        <v>6977087</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2950,6 +2945,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Årsfärska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3800,10 +3800,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130091955</v>
+        <v>130091913</v>
       </c>
       <c r="B33" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3811,21 +3811,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557821</v>
+        <v>558131</v>
       </c>
       <c r="R33" t="n">
-        <v>6977051</v>
+        <v>6977156</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3871,6 +3871,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3897,10 +3902,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130091970</v>
+        <v>130091898</v>
       </c>
       <c r="B34" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3908,19 +3913,23 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3928,10 +3937,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>557600</v>
+        <v>557607</v>
       </c>
       <c r="R34" t="n">
-        <v>6977180</v>
+        <v>6977172</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3964,6 +3973,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3990,7 +4004,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130091913</v>
+        <v>130091919</v>
       </c>
       <c r="B35" t="n">
         <v>57826</v>
@@ -4025,10 +4039,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558131</v>
+        <v>558105</v>
       </c>
       <c r="R35" t="n">
-        <v>6977156</v>
+        <v>6977169</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,7 +4106,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130091898</v>
+        <v>130091915</v>
       </c>
       <c r="B36" t="n">
         <v>57826</v>
@@ -4127,10 +4141,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557607</v>
+        <v>558130</v>
       </c>
       <c r="R36" t="n">
-        <v>6977172</v>
+        <v>6977157</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4167,7 +4181,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4194,10 +4208,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130091919</v>
+        <v>130091955</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4205,21 +4219,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4229,10 +4243,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558105</v>
+        <v>557821</v>
       </c>
       <c r="R37" t="n">
-        <v>6977169</v>
+        <v>6977051</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4265,11 +4279,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4296,10 +4305,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130091915</v>
+        <v>130091970</v>
       </c>
       <c r="B38" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4307,23 +4316,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4331,10 +4336,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558130</v>
+        <v>557600</v>
       </c>
       <c r="R38" t="n">
-        <v>6977157</v>
+        <v>6977180</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4367,11 +4372,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4398,10 +4398,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130091942</v>
+        <v>130091895</v>
       </c>
       <c r="B39" t="n">
-        <v>80286</v>
+        <v>91728</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557679</v>
+        <v>557656</v>
       </c>
       <c r="R39" t="n">
-        <v>6977024</v>
+        <v>6977218</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4495,7 +4495,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130091895</v>
+        <v>130091896</v>
       </c>
       <c r="B40" t="n">
         <v>91728</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557656</v>
+        <v>557915</v>
       </c>
       <c r="R40" t="n">
-        <v>6977218</v>
+        <v>6977133</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4592,10 +4592,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130091896</v>
+        <v>130091942</v>
       </c>
       <c r="B41" t="n">
-        <v>91728</v>
+        <v>80286</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557915</v>
+        <v>557679</v>
       </c>
       <c r="R41" t="n">
-        <v>6977133</v>
+        <v>6977024</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130091973</v>
+        <v>130091946</v>
       </c>
       <c r="B50" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557688</v>
+        <v>557850</v>
       </c>
       <c r="R50" t="n">
-        <v>6977239</v>
+        <v>6977174</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130091946</v>
+        <v>130091973</v>
       </c>
       <c r="B51" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5598,21 +5598,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557850</v>
+        <v>557688</v>
       </c>
       <c r="R51" t="n">
-        <v>6977174</v>
+        <v>6977239</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130091947</v>
+        <v>130091918</v>
       </c>
       <c r="B54" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5894,21 +5894,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558180</v>
+        <v>558109</v>
       </c>
       <c r="R54" t="n">
-        <v>6977031</v>
+        <v>6977170</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5985,10 +5985,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130091954</v>
+        <v>130091917</v>
       </c>
       <c r="B55" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5996,21 +5996,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6020,10 +6020,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557797</v>
+        <v>558129</v>
       </c>
       <c r="R55" t="n">
-        <v>6977073</v>
+        <v>6977165</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6056,6 +6056,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6082,7 +6087,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130091918</v>
+        <v>130091928</v>
       </c>
       <c r="B56" t="n">
         <v>57826</v>
@@ -6117,10 +6122,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558109</v>
+        <v>557821</v>
       </c>
       <c r="R56" t="n">
-        <v>6977170</v>
+        <v>6977048</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6184,10 +6189,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130091917</v>
+        <v>130091947</v>
       </c>
       <c r="B57" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6195,21 +6200,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6219,10 +6224,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558129</v>
+        <v>558180</v>
       </c>
       <c r="R57" t="n">
-        <v>6977165</v>
+        <v>6977031</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6259,7 +6264,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6286,10 +6291,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130091928</v>
+        <v>130091954</v>
       </c>
       <c r="B58" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6297,21 +6302,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6321,10 +6326,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557821</v>
+        <v>557797</v>
       </c>
       <c r="R58" t="n">
-        <v>6977048</v>
+        <v>6977073</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6357,11 +6362,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6388,10 +6388,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130091948</v>
+        <v>130091923</v>
       </c>
       <c r="B59" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6399,21 +6399,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558157</v>
+        <v>557985</v>
       </c>
       <c r="R59" t="n">
-        <v>6976991</v>
+        <v>6977074</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6459,6 +6459,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6485,32 +6490,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130091964</v>
+        <v>130091948</v>
       </c>
       <c r="B60" t="n">
-        <v>80321</v>
+        <v>80285</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6520,10 +6525,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>557819</v>
+        <v>558157</v>
       </c>
       <c r="R60" t="n">
-        <v>6977050</v>
+        <v>6976991</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6582,32 +6587,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130091961</v>
+        <v>130091964</v>
       </c>
       <c r="B61" t="n">
-        <v>80285</v>
+        <v>80321</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6617,10 +6622,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>557676</v>
+        <v>557819</v>
       </c>
       <c r="R61" t="n">
-        <v>6977046</v>
+        <v>6977050</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6679,10 +6684,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130091923</v>
+        <v>130091961</v>
       </c>
       <c r="B62" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6690,21 +6695,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6714,10 +6719,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>557985</v>
+        <v>557676</v>
       </c>
       <c r="R62" t="n">
-        <v>6977074</v>
+        <v>6977046</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6750,11 +6755,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6781,10 +6781,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130091971</v>
+        <v>130091953</v>
       </c>
       <c r="B63" t="n">
-        <v>91748</v>
+        <v>80285</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6792,19 +6792,23 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6812,10 +6816,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>557796</v>
+        <v>557806</v>
       </c>
       <c r="R63" t="n">
-        <v>6977175</v>
+        <v>6977127</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,32 +6878,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130091931</v>
+        <v>130091965</v>
       </c>
       <c r="B64" t="n">
-        <v>57826</v>
+        <v>80321</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6909,10 +6913,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>557736</v>
+        <v>557684</v>
       </c>
       <c r="R64" t="n">
-        <v>6977135</v>
+        <v>6977076</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6945,11 +6949,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6976,10 +6975,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130091953</v>
+        <v>130091971</v>
       </c>
       <c r="B65" t="n">
-        <v>80285</v>
+        <v>91748</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6987,23 +6986,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7011,10 +7006,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557806</v>
+        <v>557796</v>
       </c>
       <c r="R65" t="n">
-        <v>6977127</v>
+        <v>6977175</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7073,32 +7068,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130091965</v>
+        <v>130091931</v>
       </c>
       <c r="B66" t="n">
-        <v>80321</v>
+        <v>57826</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7108,10 +7103,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557684</v>
+        <v>557736</v>
       </c>
       <c r="R66" t="n">
-        <v>6977076</v>
+        <v>6977135</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7144,6 +7139,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7267,10 +7267,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130091908</v>
+        <v>130091951</v>
       </c>
       <c r="B68" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7278,21 +7278,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7302,10 +7302,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558158</v>
+        <v>558055</v>
       </c>
       <c r="R68" t="n">
-        <v>6977109</v>
+        <v>6977160</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7338,11 +7338,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7369,10 +7364,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130091900</v>
+        <v>130091969</v>
       </c>
       <c r="B69" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7380,23 +7375,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7404,10 +7395,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>557708</v>
+        <v>557703</v>
       </c>
       <c r="R69" t="n">
-        <v>6977174</v>
+        <v>6977166</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7440,11 +7431,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7471,10 +7457,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130091969</v>
+        <v>130091908</v>
       </c>
       <c r="B70" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7482,19 +7468,23 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7502,10 +7492,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>557703</v>
+        <v>558158</v>
       </c>
       <c r="R70" t="n">
-        <v>6977166</v>
+        <v>6977109</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7538,6 +7528,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7564,10 +7559,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130091951</v>
+        <v>130091900</v>
       </c>
       <c r="B71" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7575,21 +7570,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7599,10 +7594,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558055</v>
+        <v>557708</v>
       </c>
       <c r="R71" t="n">
-        <v>6977160</v>
+        <v>6977174</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7635,6 +7630,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7962,32 +7962,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130091963</v>
+        <v>130091944</v>
       </c>
       <c r="B75" t="n">
-        <v>80321</v>
+        <v>92026</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7997,10 +7997,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558184</v>
+        <v>557705</v>
       </c>
       <c r="R75" t="n">
-        <v>6977035</v>
+        <v>6977169</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8059,10 +8059,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130091944</v>
+        <v>130091941</v>
       </c>
       <c r="B76" t="n">
-        <v>92026</v>
+        <v>80286</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>557705</v>
+        <v>557676</v>
       </c>
       <c r="R76" t="n">
-        <v>6977169</v>
+        <v>6977043</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8156,32 +8156,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130091941</v>
+        <v>130091963</v>
       </c>
       <c r="B77" t="n">
-        <v>80286</v>
+        <v>80321</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557676</v>
+        <v>558184</v>
       </c>
       <c r="R77" t="n">
-        <v>6977043</v>
+        <v>6977035</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 57458-2025 artfynd.xlsx
+++ b/artfynd/A 57458-2025 artfynd.xlsx
@@ -2976,7 +2976,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130091897</v>
+        <v>130091932</v>
       </c>
       <c r="B25" t="n">
         <v>57826</v>
@@ -3005,24 +3005,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557596</v>
+        <v>557737</v>
       </c>
       <c r="R25" t="n">
-        <v>6977180</v>
+        <v>6977023</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,7 +3051,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gammalt bohål i grantickerötad högstubbe. Bohålets diameter är omkring 4,5-5 cm. Hålet sitter omkring  en meter ovan mark. I högstubben, som kanske är fem meter hög, finns omkring 4,5 fler påbörjade bohål.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3086,7 +3078,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130091901</v>
+        <v>130091897</v>
       </c>
       <c r="B26" t="n">
         <v>57826</v>
@@ -3115,16 +3107,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557649</v>
+        <v>557596</v>
       </c>
       <c r="R26" t="n">
-        <v>6977216</v>
+        <v>6977180</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Gammalt bohål i grantickerötad högstubbe. Bohålets diameter är omkring 4,5-5 cm. Hålet sitter omkring  en meter ovan mark. I högstubben, som kanske är fem meter hög, finns omkring 4,5 fler påbörjade bohål.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3188,7 +3188,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130091932</v>
+        <v>130091901</v>
       </c>
       <c r="B27" t="n">
         <v>57826</v>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557737</v>
+        <v>557649</v>
       </c>
       <c r="R27" t="n">
-        <v>6977023</v>
+        <v>6977216</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3800,10 +3800,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130091970</v>
+        <v>130091955</v>
       </c>
       <c r="B33" t="n">
-        <v>91748</v>
+        <v>80285</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3811,19 +3811,23 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3831,10 +3835,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557600</v>
+        <v>557821</v>
       </c>
       <c r="R33" t="n">
-        <v>6977180</v>
+        <v>6977051</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3995,7 +3999,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130091898</v>
+        <v>130091919</v>
       </c>
       <c r="B35" t="n">
         <v>57826</v>
@@ -4030,10 +4034,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557607</v>
+        <v>558105</v>
       </c>
       <c r="R35" t="n">
-        <v>6977172</v>
+        <v>6977169</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4070,7 +4074,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4097,7 +4101,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130091919</v>
+        <v>130091915</v>
       </c>
       <c r="B36" t="n">
         <v>57826</v>
@@ -4132,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558105</v>
+        <v>558130</v>
       </c>
       <c r="R36" t="n">
-        <v>6977169</v>
+        <v>6977157</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4199,7 +4203,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130091915</v>
+        <v>130091898</v>
       </c>
       <c r="B37" t="n">
         <v>57826</v>
@@ -4234,10 +4238,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558130</v>
+        <v>557607</v>
       </c>
       <c r="R37" t="n">
-        <v>6977157</v>
+        <v>6977172</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4274,7 +4278,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4301,10 +4305,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130091955</v>
+        <v>130091970</v>
       </c>
       <c r="B38" t="n">
-        <v>80285</v>
+        <v>91748</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4312,23 +4316,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557821</v>
+        <v>557600</v>
       </c>
       <c r="R38" t="n">
-        <v>6977051</v>
+        <v>6977180</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 57458-2025 artfynd.xlsx
+++ b/artfynd/A 57458-2025 artfynd.xlsx
@@ -1578,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130091959</v>
+        <v>130091916</v>
       </c>
       <c r="B11" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557704</v>
+        <v>558130</v>
       </c>
       <c r="R11" t="n">
-        <v>6977024</v>
+        <v>6977159</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,6 +1649,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130091952</v>
+        <v>130091911</v>
       </c>
       <c r="B12" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557819</v>
+        <v>558143</v>
       </c>
       <c r="R12" t="n">
-        <v>6977105</v>
+        <v>6977143</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,6 +1751,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1772,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130091916</v>
+        <v>130091959</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1807,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558130</v>
+        <v>557704</v>
       </c>
       <c r="R13" t="n">
-        <v>6977159</v>
+        <v>6977024</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,11 +1853,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1874,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130091911</v>
+        <v>130091952</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558143</v>
+        <v>557819</v>
       </c>
       <c r="R14" t="n">
-        <v>6977143</v>
+        <v>6977105</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,11 +1950,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2976,7 +2976,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130091932</v>
+        <v>130091897</v>
       </c>
       <c r="B25" t="n">
         <v>57826</v>
@@ -3005,16 +3005,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557737</v>
+        <v>557596</v>
       </c>
       <c r="R25" t="n">
-        <v>6977023</v>
+        <v>6977180</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,7 +3059,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Gammalt bohål i grantickerötad högstubbe. Bohålets diameter är omkring 4,5-5 cm. Hålet sitter omkring  en meter ovan mark. I högstubben, som kanske är fem meter hög, finns omkring 4,5 fler påbörjade bohål.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,7 +3086,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130091897</v>
+        <v>130091901</v>
       </c>
       <c r="B26" t="n">
         <v>57826</v>
@@ -3107,24 +3115,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557596</v>
+        <v>557649</v>
       </c>
       <c r="R26" t="n">
-        <v>6977180</v>
+        <v>6977216</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gammalt bohål i grantickerötad högstubbe. Bohålets diameter är omkring 4,5-5 cm. Hålet sitter omkring  en meter ovan mark. I högstubben, som kanske är fem meter hög, finns omkring 4,5 fler påbörjade bohål.</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3188,7 +3188,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130091901</v>
+        <v>130091932</v>
       </c>
       <c r="B27" t="n">
         <v>57826</v>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557649</v>
+        <v>557737</v>
       </c>
       <c r="R27" t="n">
-        <v>6977216</v>
+        <v>6977023</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4398,10 +4398,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130091895</v>
+        <v>130091942</v>
       </c>
       <c r="B39" t="n">
-        <v>91728</v>
+        <v>80286</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557656</v>
+        <v>557679</v>
       </c>
       <c r="R39" t="n">
-        <v>6977218</v>
+        <v>6977024</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4495,7 +4495,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130091896</v>
+        <v>130091895</v>
       </c>
       <c r="B40" t="n">
         <v>91728</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557915</v>
+        <v>557656</v>
       </c>
       <c r="R40" t="n">
-        <v>6977133</v>
+        <v>6977218</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4592,10 +4592,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130091907</v>
+        <v>130091896</v>
       </c>
       <c r="B41" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558144</v>
+        <v>557915</v>
       </c>
       <c r="R41" t="n">
-        <v>6977042</v>
+        <v>6977133</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4663,11 +4663,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4796,10 +4791,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130091942</v>
+        <v>130091907</v>
       </c>
       <c r="B43" t="n">
-        <v>80286</v>
+        <v>57826</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4807,21 +4802,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4831,10 +4826,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557679</v>
+        <v>558144</v>
       </c>
       <c r="R43" t="n">
-        <v>6977024</v>
+        <v>6977042</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,6 +4862,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130091973</v>
+        <v>130091946</v>
       </c>
       <c r="B50" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557688</v>
+        <v>557850</v>
       </c>
       <c r="R50" t="n">
-        <v>6977239</v>
+        <v>6977174</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130091946</v>
+        <v>130091973</v>
       </c>
       <c r="B51" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5598,21 +5598,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557850</v>
+        <v>557688</v>
       </c>
       <c r="R51" t="n">
-        <v>6977174</v>
+        <v>6977239</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7170,30 +7170,34 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130091969</v>
+        <v>130091943</v>
       </c>
       <c r="B67" t="n">
-        <v>91748</v>
+        <v>92181</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7201,10 +7205,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557703</v>
+        <v>557913</v>
       </c>
       <c r="R67" t="n">
-        <v>6977166</v>
+        <v>6977135</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7263,10 +7267,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130091951</v>
+        <v>130091969</v>
       </c>
       <c r="B68" t="n">
-        <v>80285</v>
+        <v>91748</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7274,23 +7278,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558055</v>
+        <v>557703</v>
       </c>
       <c r="R68" t="n">
-        <v>6977160</v>
+        <v>6977166</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7360,10 +7360,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130091908</v>
+        <v>130091951</v>
       </c>
       <c r="B69" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7371,21 +7371,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558158</v>
+        <v>558055</v>
       </c>
       <c r="R69" t="n">
-        <v>6977109</v>
+        <v>6977160</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7431,11 +7431,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7462,7 +7457,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130091900</v>
+        <v>130091908</v>
       </c>
       <c r="B70" t="n">
         <v>57826</v>
@@ -7497,10 +7492,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>557708</v>
+        <v>558158</v>
       </c>
       <c r="R70" t="n">
-        <v>6977174</v>
+        <v>6977109</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7537,7 +7532,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7564,32 +7559,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130091943</v>
+        <v>130091900</v>
       </c>
       <c r="B71" t="n">
-        <v>92181</v>
+        <v>57826</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7599,10 +7594,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>557913</v>
+        <v>557708</v>
       </c>
       <c r="R71" t="n">
-        <v>6977135</v>
+        <v>6977174</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7635,6 +7630,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 57458-2025 artfynd.xlsx
+++ b/artfynd/A 57458-2025 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130091960</v>
+        <v>130091922</v>
       </c>
       <c r="B6" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557676</v>
+        <v>558032</v>
       </c>
       <c r="R6" t="n">
-        <v>6977079</v>
+        <v>6977158</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,7 +1175,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130091922</v>
+        <v>130091909</v>
       </c>
       <c r="B7" t="n">
         <v>57826</v>
@@ -1205,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558032</v>
+        <v>558154</v>
       </c>
       <c r="R7" t="n">
-        <v>6977158</v>
+        <v>6977116</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,7 +1250,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130091909</v>
+        <v>130091904</v>
       </c>
       <c r="B8" t="n">
         <v>57826</v>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558154</v>
+        <v>557758</v>
       </c>
       <c r="R8" t="n">
-        <v>6977116</v>
+        <v>6977187</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130091904</v>
+        <v>130091926</v>
       </c>
       <c r="B9" t="n">
         <v>57826</v>
@@ -1409,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557758</v>
+        <v>557842</v>
       </c>
       <c r="R9" t="n">
-        <v>6977187</v>
+        <v>6977126</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130091926</v>
+        <v>130091960</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557842</v>
+        <v>557676</v>
       </c>
       <c r="R10" t="n">
-        <v>6977126</v>
+        <v>6977079</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1552,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130091916</v>
+        <v>130091959</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558130</v>
+        <v>557704</v>
       </c>
       <c r="R11" t="n">
-        <v>6977159</v>
+        <v>6977024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,11 +1649,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130091911</v>
+        <v>130091952</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558143</v>
+        <v>557819</v>
       </c>
       <c r="R12" t="n">
-        <v>6977143</v>
+        <v>6977105</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,11 +1746,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130091959</v>
+        <v>130091916</v>
       </c>
       <c r="B13" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557704</v>
+        <v>558130</v>
       </c>
       <c r="R13" t="n">
-        <v>6977024</v>
+        <v>6977159</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,6 +1843,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130091952</v>
+        <v>130091911</v>
       </c>
       <c r="B14" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1885,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557819</v>
+        <v>558143</v>
       </c>
       <c r="R14" t="n">
-        <v>6977105</v>
+        <v>6977143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,6 +1945,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2976,7 +2976,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130091897</v>
+        <v>130091932</v>
       </c>
       <c r="B25" t="n">
         <v>57826</v>
@@ -3005,24 +3005,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557596</v>
+        <v>557737</v>
       </c>
       <c r="R25" t="n">
-        <v>6977180</v>
+        <v>6977023</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,7 +3051,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gammalt bohål i grantickerötad högstubbe. Bohålets diameter är omkring 4,5-5 cm. Hålet sitter omkring  en meter ovan mark. I högstubben, som kanske är fem meter hög, finns omkring 4,5 fler påbörjade bohål.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3086,7 +3078,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130091901</v>
+        <v>130091897</v>
       </c>
       <c r="B26" t="n">
         <v>57826</v>
@@ -3115,16 +3107,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557649</v>
+        <v>557596</v>
       </c>
       <c r="R26" t="n">
-        <v>6977216</v>
+        <v>6977180</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Gammalt bohål i grantickerötad högstubbe. Bohålets diameter är omkring 4,5-5 cm. Hålet sitter omkring  en meter ovan mark. I högstubben, som kanske är fem meter hög, finns omkring 4,5 fler påbörjade bohål.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3188,7 +3188,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130091932</v>
+        <v>130091901</v>
       </c>
       <c r="B27" t="n">
         <v>57826</v>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557737</v>
+        <v>557649</v>
       </c>
       <c r="R27" t="n">
-        <v>6977023</v>
+        <v>6977216</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4398,10 +4398,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130091942</v>
+        <v>130091895</v>
       </c>
       <c r="B39" t="n">
-        <v>80286</v>
+        <v>91728</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557679</v>
+        <v>557656</v>
       </c>
       <c r="R39" t="n">
-        <v>6977024</v>
+        <v>6977218</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4495,7 +4495,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130091895</v>
+        <v>130091896</v>
       </c>
       <c r="B40" t="n">
         <v>91728</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557656</v>
+        <v>557915</v>
       </c>
       <c r="R40" t="n">
-        <v>6977218</v>
+        <v>6977133</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4592,10 +4592,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130091896</v>
+        <v>130091907</v>
       </c>
       <c r="B41" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557915</v>
+        <v>558144</v>
       </c>
       <c r="R41" t="n">
-        <v>6977133</v>
+        <v>6977042</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4663,6 +4663,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4791,10 +4796,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130091907</v>
+        <v>130091942</v>
       </c>
       <c r="B43" t="n">
-        <v>57826</v>
+        <v>80286</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4802,21 +4807,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4826,10 +4831,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558144</v>
+        <v>557679</v>
       </c>
       <c r="R43" t="n">
-        <v>6977042</v>
+        <v>6977024</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4862,11 +4867,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -8059,32 +8059,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130091963</v>
+        <v>130091941</v>
       </c>
       <c r="B76" t="n">
-        <v>80321</v>
+        <v>80286</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558184</v>
+        <v>557676</v>
       </c>
       <c r="R76" t="n">
-        <v>6977035</v>
+        <v>6977043</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8156,32 +8156,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130091941</v>
+        <v>130091963</v>
       </c>
       <c r="B77" t="n">
-        <v>80286</v>
+        <v>80321</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557676</v>
+        <v>558184</v>
       </c>
       <c r="R77" t="n">
-        <v>6977043</v>
+        <v>6977035</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 57458-2025 artfynd.xlsx
+++ b/artfynd/A 57458-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130091975</v>
+        <v>130091944</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557681</v>
+        <v>557705</v>
       </c>
       <c r="R2" t="n">
-        <v>6977020</v>
+        <v>6977169</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130091945</v>
+        <v>130091968</v>
       </c>
       <c r="B3" t="n">
-        <v>80285</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557675</v>
+        <v>557647</v>
       </c>
       <c r="R3" t="n">
-        <v>6977245</v>
+        <v>6977216</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130091906</v>
+        <v>130091895</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558128</v>
+        <v>557656</v>
       </c>
       <c r="R4" t="n">
-        <v>6976972</v>
+        <v>6977218</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130091934</v>
+        <v>130091896</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557686</v>
+        <v>557915</v>
       </c>
       <c r="R5" t="n">
-        <v>6977106</v>
+        <v>6977133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130091922</v>
+        <v>130091943</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558032</v>
+        <v>557913</v>
       </c>
       <c r="R6" t="n">
-        <v>6977158</v>
+        <v>6977135</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130091909</v>
+        <v>130091941</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558154</v>
+        <v>557676</v>
       </c>
       <c r="R7" t="n">
-        <v>6977116</v>
+        <v>6977043</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130091904</v>
+        <v>130091942</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557758</v>
+        <v>557679</v>
       </c>
       <c r="R8" t="n">
-        <v>6977187</v>
+        <v>6977024</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,11 +1328,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130091926</v>
+        <v>130091973</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557842</v>
+        <v>557688</v>
       </c>
       <c r="R9" t="n">
-        <v>6977126</v>
+        <v>6977239</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1450,11 +1425,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130091960</v>
+        <v>130091974</v>
       </c>
       <c r="B10" t="n">
-        <v>80285</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557676</v>
+        <v>557715</v>
       </c>
       <c r="R10" t="n">
-        <v>6977079</v>
+        <v>6977026</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130091959</v>
+        <v>130091975</v>
       </c>
       <c r="B11" t="n">
-        <v>80285</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557704</v>
+        <v>557681</v>
       </c>
       <c r="R11" t="n">
-        <v>6977024</v>
+        <v>6977020</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130091952</v>
+        <v>130091945</v>
       </c>
       <c r="B12" t="n">
-        <v>80285</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557819</v>
+        <v>557675</v>
       </c>
       <c r="R12" t="n">
-        <v>6977105</v>
+        <v>6977245</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1772,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130091916</v>
+        <v>130091946</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1807,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558130</v>
+        <v>557850</v>
       </c>
       <c r="R13" t="n">
-        <v>6977159</v>
+        <v>6977174</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,11 +1813,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1874,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130091911</v>
+        <v>130091947</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558143</v>
+        <v>558180</v>
       </c>
       <c r="R14" t="n">
-        <v>6977143</v>
+        <v>6977031</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,7 +1914,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130091967</v>
+        <v>130091948</v>
       </c>
       <c r="B15" t="n">
-        <v>80321</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557677</v>
+        <v>558157</v>
       </c>
       <c r="R15" t="n">
-        <v>6977026</v>
+        <v>6976991</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130091933</v>
+        <v>130091949</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2084,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2108,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557693</v>
+        <v>558142</v>
       </c>
       <c r="R16" t="n">
-        <v>6977096</v>
+        <v>6977034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2144,11 +2109,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2175,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130091924</v>
+        <v>130091950</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2210,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557902</v>
+        <v>558152</v>
       </c>
       <c r="R17" t="n">
-        <v>6977133</v>
+        <v>6977036</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2246,11 +2206,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2277,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130091903</v>
+        <v>130091951</v>
       </c>
       <c r="B18" t="n">
-        <v>57826</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>557678</v>
+        <v>558055</v>
       </c>
       <c r="R18" t="n">
-        <v>6977236</v>
+        <v>6977160</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2303,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130091930</v>
+        <v>130091952</v>
       </c>
       <c r="B19" t="n">
-        <v>57826</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557797</v>
+        <v>557819</v>
       </c>
       <c r="R19" t="n">
-        <v>6977045</v>
+        <v>6977105</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2450,11 +2400,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130091950</v>
+        <v>130091953</v>
       </c>
       <c r="B20" t="n">
-        <v>80285</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2516,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558152</v>
+        <v>557806</v>
       </c>
       <c r="R20" t="n">
-        <v>6977036</v>
+        <v>6977127</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2578,10 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130091962</v>
+        <v>130091954</v>
       </c>
       <c r="B21" t="n">
-        <v>80285</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2613,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557678</v>
+        <v>557797</v>
       </c>
       <c r="R21" t="n">
-        <v>6977026</v>
+        <v>6977073</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130091956</v>
+        <v>130091955</v>
       </c>
       <c r="B22" t="n">
-        <v>80285</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2710,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557820</v>
+        <v>557821</v>
       </c>
       <c r="R22" t="n">
-        <v>6977049</v>
+        <v>6977051</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130091938</v>
+        <v>130091956</v>
       </c>
       <c r="B23" t="n">
-        <v>57826</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557679</v>
+        <v>557820</v>
       </c>
       <c r="R23" t="n">
-        <v>6977111</v>
+        <v>6977049</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2788,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2874,10 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130091940</v>
+        <v>130091957</v>
       </c>
       <c r="B24" t="n">
-        <v>57826</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2825,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557675</v>
+        <v>557818</v>
       </c>
       <c r="R24" t="n">
-        <v>6977087</v>
+        <v>6977041</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,11 +2885,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Årsfärska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130091932</v>
+        <v>130091958</v>
       </c>
       <c r="B25" t="n">
-        <v>57826</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3011,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557737</v>
+        <v>557811</v>
       </c>
       <c r="R25" t="n">
-        <v>6977023</v>
+        <v>6977031</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3047,11 +2982,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130091897</v>
+        <v>130091959</v>
       </c>
       <c r="B26" t="n">
-        <v>57826</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,42 +3019,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557596</v>
+        <v>557704</v>
       </c>
       <c r="R26" t="n">
-        <v>6977180</v>
+        <v>6977024</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3157,11 +3079,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gammalt bohål i grantickerötad högstubbe. Bohålets diameter är omkring 4,5-5 cm. Hålet sitter omkring  en meter ovan mark. I högstubben, som kanske är fem meter hög, finns omkring 4,5 fler påbörjade bohål.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3188,10 +3105,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130091901</v>
+        <v>130091960</v>
       </c>
       <c r="B27" t="n">
-        <v>57826</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3199,21 +3116,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3223,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557649</v>
+        <v>557676</v>
       </c>
       <c r="R27" t="n">
-        <v>6977216</v>
+        <v>6977079</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3259,11 +3176,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3290,10 +3202,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130091910</v>
+        <v>130091961</v>
       </c>
       <c r="B28" t="n">
-        <v>57826</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3301,21 +3213,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3325,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558157</v>
+        <v>557676</v>
       </c>
       <c r="R28" t="n">
-        <v>6977119</v>
+        <v>6977046</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3361,11 +3273,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3392,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130091899</v>
+        <v>130091962</v>
       </c>
       <c r="B29" t="n">
-        <v>57826</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3403,21 +3310,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3427,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557634</v>
+        <v>557678</v>
       </c>
       <c r="R29" t="n">
-        <v>6977186</v>
+        <v>6977026</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3463,11 +3370,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3494,32 +3396,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130091905</v>
+        <v>130091963</v>
       </c>
       <c r="B30" t="n">
-        <v>57826</v>
+        <v>80468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3529,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558162</v>
+        <v>558184</v>
       </c>
       <c r="R30" t="n">
-        <v>6977113</v>
+        <v>6977035</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3565,11 +3467,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3596,32 +3493,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130091927</v>
+        <v>130091964</v>
       </c>
       <c r="B31" t="n">
-        <v>57826</v>
+        <v>80468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3631,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557821</v>
+        <v>557819</v>
       </c>
       <c r="R31" t="n">
-        <v>6977051</v>
+        <v>6977050</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3667,11 +3564,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3698,32 +3590,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130091929</v>
+        <v>130091965</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>80468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3733,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557813</v>
+        <v>557684</v>
       </c>
       <c r="R32" t="n">
-        <v>6977043</v>
+        <v>6977076</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3769,11 +3661,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Kommer lite kåda ur några hål varför jag rapporterar dem som färska.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3800,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130091955</v>
+        <v>130091966</v>
       </c>
       <c r="B33" t="n">
-        <v>80285</v>
+        <v>80468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3835,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557821</v>
+        <v>557775</v>
       </c>
       <c r="R33" t="n">
-        <v>6977051</v>
+        <v>6977068</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3897,32 +3784,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130091913</v>
+        <v>130091967</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>80468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3932,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558131</v>
+        <v>557677</v>
       </c>
       <c r="R34" t="n">
-        <v>6977156</v>
+        <v>6977026</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3968,11 +3855,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3999,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130091919</v>
+        <v>130091897</v>
       </c>
       <c r="B35" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4028,16 +3910,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558105</v>
+        <v>557596</v>
       </c>
       <c r="R35" t="n">
-        <v>6977169</v>
+        <v>6977180</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4074,7 +3964,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Gammalt bohål i grantickerötad högstubbe. Bohålets diameter är omkring 4,5-5 cm. Hålet sitter omkring  en meter ovan mark. I högstubben, som kanske är fem meter hög, finns omkring 4,5 fler påbörjade bohål.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4101,10 +3991,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130091915</v>
+        <v>130091898</v>
       </c>
       <c r="B36" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4136,10 +4026,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558130</v>
+        <v>557607</v>
       </c>
       <c r="R36" t="n">
-        <v>6977157</v>
+        <v>6977172</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4176,7 +4066,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4203,10 +4093,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130091898</v>
+        <v>130091899</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4238,10 +4128,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557607</v>
+        <v>557634</v>
       </c>
       <c r="R37" t="n">
-        <v>6977172</v>
+        <v>6977186</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4278,7 +4168,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4305,10 +4195,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130091970</v>
+        <v>130091900</v>
       </c>
       <c r="B38" t="n">
-        <v>91748</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4316,19 +4206,23 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4336,10 +4230,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557600</v>
+        <v>557708</v>
       </c>
       <c r="R38" t="n">
-        <v>6977180</v>
+        <v>6977174</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4372,6 +4266,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4398,10 +4297,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130091895</v>
+        <v>130091901</v>
       </c>
       <c r="B39" t="n">
-        <v>91728</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,21 +4308,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4332,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557656</v>
+        <v>557649</v>
       </c>
       <c r="R39" t="n">
-        <v>6977218</v>
+        <v>6977216</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4469,6 +4368,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4495,10 +4399,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130091896</v>
+        <v>130091902</v>
       </c>
       <c r="B40" t="n">
-        <v>91728</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4506,21 +4410,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4530,10 +4434,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557915</v>
+        <v>557666</v>
       </c>
       <c r="R40" t="n">
-        <v>6977133</v>
+        <v>6977240</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4566,6 +4470,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4592,10 +4501,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130091907</v>
+        <v>130091903</v>
       </c>
       <c r="B41" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4627,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558144</v>
+        <v>557678</v>
       </c>
       <c r="R41" t="n">
-        <v>6977042</v>
+        <v>6977236</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4694,10 +4603,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130091925</v>
+        <v>130091904</v>
       </c>
       <c r="B42" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4729,10 +4638,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557904</v>
+        <v>557758</v>
       </c>
       <c r="R42" t="n">
-        <v>6977140</v>
+        <v>6977187</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4796,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130091942</v>
+        <v>130091905</v>
       </c>
       <c r="B43" t="n">
-        <v>80286</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4807,21 +4716,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4831,10 +4740,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557679</v>
+        <v>558162</v>
       </c>
       <c r="R43" t="n">
-        <v>6977024</v>
+        <v>6977113</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,6 +4776,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4893,10 +4807,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130091949</v>
+        <v>130091906</v>
       </c>
       <c r="B44" t="n">
-        <v>80285</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4904,21 +4818,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4928,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558142</v>
+        <v>558128</v>
       </c>
       <c r="R44" t="n">
-        <v>6977034</v>
+        <v>6976972</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,6 +4878,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4990,32 +4909,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130091966</v>
+        <v>130091907</v>
       </c>
       <c r="B45" t="n">
-        <v>80321</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5025,10 +4944,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557775</v>
+        <v>558144</v>
       </c>
       <c r="R45" t="n">
-        <v>6977068</v>
+        <v>6977042</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,6 +4980,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5087,10 +5011,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130091921</v>
+        <v>130091908</v>
       </c>
       <c r="B46" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5122,10 +5046,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558051</v>
+        <v>558158</v>
       </c>
       <c r="R46" t="n">
-        <v>6977156</v>
+        <v>6977109</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5189,10 +5113,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130091939</v>
+        <v>130091909</v>
       </c>
       <c r="B47" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5224,10 +5148,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557682</v>
+        <v>558154</v>
       </c>
       <c r="R47" t="n">
-        <v>6977094</v>
+        <v>6977116</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,10 +5215,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130091974</v>
+        <v>130091910</v>
       </c>
       <c r="B48" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5302,21 +5226,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5326,10 +5250,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557715</v>
+        <v>558157</v>
       </c>
       <c r="R48" t="n">
-        <v>6977026</v>
+        <v>6977119</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5362,6 +5286,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5388,10 +5317,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130091912</v>
+        <v>130091911</v>
       </c>
       <c r="B49" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5423,10 +5352,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558132</v>
+        <v>558143</v>
       </c>
       <c r="R49" t="n">
-        <v>6977158</v>
+        <v>6977143</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5490,10 +5419,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130091946</v>
+        <v>130091912</v>
       </c>
       <c r="B50" t="n">
-        <v>80285</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5501,21 +5430,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5525,10 +5454,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557850</v>
+        <v>558132</v>
       </c>
       <c r="R50" t="n">
-        <v>6977174</v>
+        <v>6977158</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5561,6 +5490,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5587,10 +5521,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130091973</v>
+        <v>130091913</v>
       </c>
       <c r="B51" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5598,21 +5532,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5622,10 +5556,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557688</v>
+        <v>558131</v>
       </c>
       <c r="R51" t="n">
-        <v>6977239</v>
+        <v>6977156</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5658,6 +5592,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5684,10 +5623,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130091936</v>
+        <v>130091915</v>
       </c>
       <c r="B52" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5719,10 +5658,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557684</v>
+        <v>558130</v>
       </c>
       <c r="R52" t="n">
-        <v>6977104</v>
+        <v>6977157</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5786,10 +5725,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130091947</v>
+        <v>130091916</v>
       </c>
       <c r="B53" t="n">
-        <v>80285</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5797,21 +5736,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5821,10 +5760,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558180</v>
+        <v>558130</v>
       </c>
       <c r="R53" t="n">
-        <v>6977031</v>
+        <v>6977159</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5861,7 +5800,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5888,10 +5827,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130091954</v>
+        <v>130091917</v>
       </c>
       <c r="B54" t="n">
-        <v>80285</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5899,21 +5838,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5923,10 +5862,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557797</v>
+        <v>558129</v>
       </c>
       <c r="R54" t="n">
-        <v>6977073</v>
+        <v>6977165</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5959,6 +5898,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5988,7 +5932,7 @@
         <v>130091918</v>
       </c>
       <c r="B55" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6087,10 +6031,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130091917</v>
+        <v>130091919</v>
       </c>
       <c r="B56" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6122,10 +6066,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558129</v>
+        <v>558105</v>
       </c>
       <c r="R56" t="n">
-        <v>6977165</v>
+        <v>6977169</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6189,10 +6133,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130091928</v>
+        <v>130091920</v>
       </c>
       <c r="B57" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6224,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557821</v>
+        <v>558063</v>
       </c>
       <c r="R57" t="n">
-        <v>6977048</v>
+        <v>6977173</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6291,10 +6235,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130091968</v>
+        <v>130091921</v>
       </c>
       <c r="B58" t="n">
-        <v>91724</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6302,21 +6246,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6326,10 +6270,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557647</v>
+        <v>558051</v>
       </c>
       <c r="R58" t="n">
-        <v>6977216</v>
+        <v>6977156</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6362,6 +6306,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6388,10 +6337,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130091948</v>
+        <v>130091922</v>
       </c>
       <c r="B59" t="n">
-        <v>80285</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6399,21 +6348,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6423,10 +6372,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558157</v>
+        <v>558032</v>
       </c>
       <c r="R59" t="n">
-        <v>6976991</v>
+        <v>6977158</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6459,6 +6408,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6485,32 +6439,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130091964</v>
+        <v>130091923</v>
       </c>
       <c r="B60" t="n">
-        <v>80321</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6520,10 +6474,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>557819</v>
+        <v>557985</v>
       </c>
       <c r="R60" t="n">
-        <v>6977050</v>
+        <v>6977074</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,6 +6510,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6582,10 +6541,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130091961</v>
+        <v>130091924</v>
       </c>
       <c r="B61" t="n">
-        <v>80285</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6593,21 +6552,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6617,10 +6576,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>557676</v>
+        <v>557902</v>
       </c>
       <c r="R61" t="n">
-        <v>6977046</v>
+        <v>6977133</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6653,6 +6612,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6679,10 +6643,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130091923</v>
+        <v>130091925</v>
       </c>
       <c r="B62" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6714,10 +6678,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>557985</v>
+        <v>557904</v>
       </c>
       <c r="R62" t="n">
-        <v>6977074</v>
+        <v>6977140</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6781,10 +6745,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130091971</v>
+        <v>130091926</v>
       </c>
       <c r="B63" t="n">
-        <v>91748</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6792,19 +6756,23 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6812,10 +6780,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>557796</v>
+        <v>557842</v>
       </c>
       <c r="R63" t="n">
-        <v>6977175</v>
+        <v>6977126</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6848,6 +6816,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6874,10 +6847,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130091953</v>
+        <v>130091927</v>
       </c>
       <c r="B64" t="n">
-        <v>80285</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6885,21 +6858,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6909,10 +6882,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>557806</v>
+        <v>557821</v>
       </c>
       <c r="R64" t="n">
-        <v>6977127</v>
+        <v>6977051</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6945,6 +6918,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6971,32 +6949,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130091965</v>
+        <v>130091928</v>
       </c>
       <c r="B65" t="n">
-        <v>80321</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7006,10 +6984,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557684</v>
+        <v>557821</v>
       </c>
       <c r="R65" t="n">
-        <v>6977076</v>
+        <v>6977048</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7042,6 +7020,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7068,10 +7051,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130091931</v>
+        <v>130091929</v>
       </c>
       <c r="B66" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7103,10 +7086,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>557736</v>
+        <v>557813</v>
       </c>
       <c r="R66" t="n">
-        <v>6977135</v>
+        <v>6977043</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7143,7 +7126,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall. Kommer lite kåda ur några hål varför jag rapporterar dem som färska.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7170,32 +7153,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130091943</v>
+        <v>130091930</v>
       </c>
       <c r="B67" t="n">
-        <v>92181</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7205,10 +7188,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>557913</v>
+        <v>557797</v>
       </c>
       <c r="R67" t="n">
-        <v>6977135</v>
+        <v>6977045</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7241,6 +7224,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7267,10 +7255,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130091969</v>
+        <v>130091931</v>
       </c>
       <c r="B68" t="n">
-        <v>91748</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7278,19 +7266,23 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7298,10 +7290,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>557703</v>
+        <v>557736</v>
       </c>
       <c r="R68" t="n">
-        <v>6977166</v>
+        <v>6977135</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7334,6 +7326,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7360,10 +7357,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130091951</v>
+        <v>130091932</v>
       </c>
       <c r="B69" t="n">
-        <v>80285</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7371,21 +7368,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7395,10 +7392,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558055</v>
+        <v>557737</v>
       </c>
       <c r="R69" t="n">
-        <v>6977160</v>
+        <v>6977023</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7431,6 +7428,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7457,10 +7459,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130091908</v>
+        <v>130091933</v>
       </c>
       <c r="B70" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7492,10 +7494,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558158</v>
+        <v>557693</v>
       </c>
       <c r="R70" t="n">
-        <v>6977109</v>
+        <v>6977096</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7532,7 +7534,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7559,10 +7561,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130091900</v>
+        <v>130091934</v>
       </c>
       <c r="B71" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7594,10 +7596,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>557708</v>
+        <v>557686</v>
       </c>
       <c r="R71" t="n">
-        <v>6977174</v>
+        <v>6977106</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7661,10 +7663,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130091920</v>
+        <v>130091936</v>
       </c>
       <c r="B72" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7696,10 +7698,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558063</v>
+        <v>557684</v>
       </c>
       <c r="R72" t="n">
-        <v>6977173</v>
+        <v>6977104</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7763,10 +7765,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130091902</v>
+        <v>130091938</v>
       </c>
       <c r="B73" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7798,10 +7800,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>557666</v>
+        <v>557679</v>
       </c>
       <c r="R73" t="n">
-        <v>6977240</v>
+        <v>6977111</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7838,7 +7840,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7865,10 +7867,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130091957</v>
+        <v>130091939</v>
       </c>
       <c r="B74" t="n">
-        <v>80285</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7876,21 +7878,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7900,10 +7902,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>557818</v>
+        <v>557682</v>
       </c>
       <c r="R74" t="n">
-        <v>6977041</v>
+        <v>6977094</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7936,6 +7938,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7962,10 +7969,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130091944</v>
+        <v>130091940</v>
       </c>
       <c r="B75" t="n">
-        <v>92026</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7973,21 +7980,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7997,10 +8004,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557705</v>
+        <v>557675</v>
       </c>
       <c r="R75" t="n">
-        <v>6977169</v>
+        <v>6977087</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8035,6 +8042,11 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Årsfärska</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8056,200 +8068,6 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>130091941</v>
-      </c>
-      <c r="B76" t="n">
-        <v>80286</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Långtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>557676</v>
-      </c>
-      <c r="R76" t="n">
-        <v>6977043</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Hällesjö</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>130091963</v>
-      </c>
-      <c r="B77" t="n">
-        <v>80321</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Långtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>558184</v>
-      </c>
-      <c r="R77" t="n">
-        <v>6977035</v>
-      </c>
-      <c r="S77" t="n">
-        <v>10</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Hällesjö</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
